--- a/Armada_Consultant_Splits.xlsx
+++ b/Armada_Consultant_Splits.xlsx
@@ -11,14 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IDS Mapping" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Investor Allocation" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consultant Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="GP_FundMgmt_Pct">Inputs!$B$5</definedName>
     <definedName name="GP_Consultant_Pct">Inputs!$B$6</definedName>
     <definedName name="GP_Raj_Pct">Inputs!$B$7</definedName>
     <definedName name="GP_Nairne_Pct">Inputs!$B$8</definedName>
-    <definedName name="GP_Phil_Pct">Inputs!$B$9</definedName>
+    <definedName name="GP_Alec_Pct">Inputs!$B$9</definedName>
     <definedName name="Expense_Pool">Inputs!$B$14</definedName>
     <definedName name="IDS_TPA">'IDS Mapping'!$A$2:$A$52</definedName>
     <definedName name="IDS_Consultant">'IDS Mapping'!$D$2:$D$52</definedName>
@@ -27,6 +28,7 @@
     <definedName name="PI_ConsultantCut">'Per-Investor Allocation'!$I$2:$I$52</definedName>
     <definedName name="PI_FundMgmt">'Per-Investor Allocation'!$H$2:$H$52</definedName>
     <definedName name="PI_Capital">'Per-Investor Allocation'!$E$2:$E$52</definedName>
+    <definedName name="Costs_Total">Costs!$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -128,14 +130,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -143,11 +145,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,7 +588,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Alec (GP)</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -612,11 +616,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Operating expenses (consultant pro-rata)</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>0</v>
+          <t>Operating expenses (live-linked to Costs sheet)</t>
+        </is>
+      </c>
+      <c r="B14" s="6">
+        <f>Costs_Total</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2091,7 +2096,7 @@
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Alec (GP)</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
@@ -2124,7 +2129,7 @@
       <c r="F2" s="9" t="n">
         <v>52197.71</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="10" t="n">
         <v>15659.31</v>
       </c>
       <c r="H2" s="9">
@@ -2144,7 +2149,7 @@
         <v/>
       </c>
       <c r="L2" s="9">
-        <f>G2*GP_Phil_Pct</f>
+        <f>G2*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M2" s="9">
@@ -2176,7 +2181,7 @@
       <c r="F3" s="9" t="n">
         <v>50530.69</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="10" t="n">
         <v>15159.21</v>
       </c>
       <c r="H3" s="9">
@@ -2196,7 +2201,7 @@
         <v/>
       </c>
       <c r="L3" s="9">
-        <f>G3*GP_Phil_Pct</f>
+        <f>G3*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M3" s="9">
@@ -2228,7 +2233,7 @@
       <c r="F4" s="9" t="n">
         <v>29883.38</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="10" t="n">
         <v>8965.01</v>
       </c>
       <c r="H4" s="9">
@@ -2248,7 +2253,7 @@
         <v/>
       </c>
       <c r="L4" s="9">
-        <f>G4*GP_Phil_Pct</f>
+        <f>G4*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M4" s="9">
@@ -2280,7 +2285,7 @@
       <c r="F5" s="9" t="n">
         <v>26262.48</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="10" t="n">
         <v>7878.74</v>
       </c>
       <c r="H5" s="9">
@@ -2300,7 +2305,7 @@
         <v/>
       </c>
       <c r="L5" s="9">
-        <f>G5*GP_Phil_Pct</f>
+        <f>G5*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M5" s="9">
@@ -2332,7 +2337,7 @@
       <c r="F6" s="9" t="n">
         <v>24752.48</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="10" t="n">
         <v>7425.74</v>
       </c>
       <c r="H6" s="9">
@@ -2352,7 +2357,7 @@
         <v/>
       </c>
       <c r="L6" s="9">
-        <f>G6*GP_Phil_Pct</f>
+        <f>G6*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M6" s="9">
@@ -2384,7 +2389,7 @@
       <c r="F7" s="9" t="n">
         <v>17887.72</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="10" t="n">
         <v>5366.32</v>
       </c>
       <c r="H7" s="9">
@@ -2404,7 +2409,7 @@
         <v/>
       </c>
       <c r="L7" s="9">
-        <f>G7*GP_Phil_Pct</f>
+        <f>G7*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M7" s="9">
@@ -2436,7 +2441,7 @@
       <c r="F8" s="9" t="n">
         <v>14775.09</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="10" t="n">
         <v>4432.53</v>
       </c>
       <c r="H8" s="9">
@@ -2456,7 +2461,7 @@
         <v/>
       </c>
       <c r="L8" s="9">
-        <f>G8*GP_Phil_Pct</f>
+        <f>G8*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M8" s="9">
@@ -2488,7 +2493,7 @@
       <c r="F9" s="9" t="n">
         <v>12445.73</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="10" t="n">
         <v>3733.72</v>
       </c>
       <c r="H9" s="9">
@@ -2508,7 +2513,7 @@
         <v/>
       </c>
       <c r="L9" s="9">
-        <f>G9*GP_Phil_Pct</f>
+        <f>G9*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M9" s="9">
@@ -2540,7 +2545,7 @@
       <c r="F10" s="9" t="n">
         <v>8580.120000000001</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="10" t="n">
         <v>2574.04</v>
       </c>
       <c r="H10" s="9">
@@ -2560,7 +2565,7 @@
         <v/>
       </c>
       <c r="L10" s="9">
-        <f>G10*GP_Phil_Pct</f>
+        <f>G10*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M10" s="9">
@@ -2592,7 +2597,7 @@
       <c r="F11" s="9" t="n">
         <v>8488.959999999999</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="10" t="n">
         <v>2546.69</v>
       </c>
       <c r="H11" s="9">
@@ -2612,7 +2617,7 @@
         <v/>
       </c>
       <c r="L11" s="9">
-        <f>G11*GP_Phil_Pct</f>
+        <f>G11*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M11" s="9">
@@ -2644,7 +2649,7 @@
       <c r="F12" s="9" t="n">
         <v>6949.9</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="10" t="n">
         <v>2084.97</v>
       </c>
       <c r="H12" s="9">
@@ -2664,7 +2669,7 @@
         <v/>
       </c>
       <c r="L12" s="9">
-        <f>G12*GP_Phil_Pct</f>
+        <f>G12*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M12" s="9">
@@ -2696,7 +2701,7 @@
       <c r="F13" s="9" t="n">
         <v>6946.34</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="10" t="n">
         <v>2083.9</v>
       </c>
       <c r="H13" s="9">
@@ -2716,7 +2721,7 @@
         <v/>
       </c>
       <c r="L13" s="9">
-        <f>G13*GP_Phil_Pct</f>
+        <f>G13*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M13" s="9">
@@ -2748,7 +2753,7 @@
       <c r="F14" s="9" t="n">
         <v>6890.08</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="10" t="n">
         <v>2067.02</v>
       </c>
       <c r="H14" s="9">
@@ -2768,7 +2773,7 @@
         <v/>
       </c>
       <c r="L14" s="9">
-        <f>G14*GP_Phil_Pct</f>
+        <f>G14*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M14" s="9">
@@ -2800,7 +2805,7 @@
       <c r="F15" s="9" t="n">
         <v>6318.31</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="10" t="n">
         <v>1895.49</v>
       </c>
       <c r="H15" s="9">
@@ -2820,7 +2825,7 @@
         <v/>
       </c>
       <c r="L15" s="9">
-        <f>G15*GP_Phil_Pct</f>
+        <f>G15*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M15" s="9">
@@ -2852,7 +2857,7 @@
       <c r="F16" s="9" t="n">
         <v>6094.66</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="10" t="n">
         <v>1828.4</v>
       </c>
       <c r="H16" s="9">
@@ -2872,7 +2877,7 @@
         <v/>
       </c>
       <c r="L16" s="9">
-        <f>G16*GP_Phil_Pct</f>
+        <f>G16*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M16" s="9">
@@ -2904,7 +2909,7 @@
       <c r="F17" s="9" t="n">
         <v>5620.33</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="10" t="n">
         <v>1686.1</v>
       </c>
       <c r="H17" s="9">
@@ -2924,7 +2929,7 @@
         <v/>
       </c>
       <c r="L17" s="9">
-        <f>G17*GP_Phil_Pct</f>
+        <f>G17*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M17" s="9">
@@ -2956,7 +2961,7 @@
       <c r="F18" s="9" t="n">
         <v>5225.49</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="10" t="n">
         <v>1567.65</v>
       </c>
       <c r="H18" s="9">
@@ -2976,7 +2981,7 @@
         <v/>
       </c>
       <c r="L18" s="9">
-        <f>G18*GP_Phil_Pct</f>
+        <f>G18*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M18" s="9">
@@ -3008,7 +3013,7 @@
       <c r="F19" s="9" t="n">
         <v>5158.19</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="10" t="n">
         <v>1547.46</v>
       </c>
       <c r="H19" s="9">
@@ -3028,7 +3033,7 @@
         <v/>
       </c>
       <c r="L19" s="9">
-        <f>G19*GP_Phil_Pct</f>
+        <f>G19*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M19" s="9">
@@ -3060,7 +3065,7 @@
       <c r="F20" s="9" t="n">
         <v>5003.8</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="10" t="n">
         <v>1501.14</v>
       </c>
       <c r="H20" s="9">
@@ -3080,7 +3085,7 @@
         <v/>
       </c>
       <c r="L20" s="9">
-        <f>G20*GP_Phil_Pct</f>
+        <f>G20*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M20" s="9">
@@ -3112,7 +3117,7 @@
       <c r="F21" s="9" t="n">
         <v>4414.13</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="10" t="n">
         <v>1324.24</v>
       </c>
       <c r="H21" s="9">
@@ -3132,7 +3137,7 @@
         <v/>
       </c>
       <c r="L21" s="9">
-        <f>G21*GP_Phil_Pct</f>
+        <f>G21*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M21" s="9">
@@ -3164,7 +3169,7 @@
       <c r="F22" s="9" t="n">
         <v>4166.44</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="10" t="n">
         <v>1249.93</v>
       </c>
       <c r="H22" s="9">
@@ -3184,7 +3189,7 @@
         <v/>
       </c>
       <c r="L22" s="9">
-        <f>G22*GP_Phil_Pct</f>
+        <f>G22*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M22" s="9">
@@ -3216,7 +3221,7 @@
       <c r="F23" s="9" t="n">
         <v>4051.74</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="10" t="n">
         <v>1215.52</v>
       </c>
       <c r="H23" s="9">
@@ -3236,7 +3241,7 @@
         <v/>
       </c>
       <c r="L23" s="9">
-        <f>G23*GP_Phil_Pct</f>
+        <f>G23*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M23" s="9">
@@ -3268,7 +3273,7 @@
       <c r="F24" s="9" t="n">
         <v>3938.27</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="10" t="n">
         <v>1181.48</v>
       </c>
       <c r="H24" s="9">
@@ -3288,7 +3293,7 @@
         <v/>
       </c>
       <c r="L24" s="9">
-        <f>G24*GP_Phil_Pct</f>
+        <f>G24*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M24" s="9">
@@ -3320,7 +3325,7 @@
       <c r="F25" s="9" t="n">
         <v>3929.79</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="10" t="n">
         <v>1178.94</v>
       </c>
       <c r="H25" s="9">
@@ -3340,7 +3345,7 @@
         <v/>
       </c>
       <c r="L25" s="9">
-        <f>G25*GP_Phil_Pct</f>
+        <f>G25*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M25" s="9">
@@ -3372,7 +3377,7 @@
       <c r="F26" s="9" t="n">
         <v>3882.37</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="10" t="n">
         <v>1164.71</v>
       </c>
       <c r="H26" s="9">
@@ -3392,7 +3397,7 @@
         <v/>
       </c>
       <c r="L26" s="9">
-        <f>G26*GP_Phil_Pct</f>
+        <f>G26*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M26" s="9">
@@ -3424,7 +3429,7 @@
       <c r="F27" s="9" t="n">
         <v>3856.11</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="10" t="n">
         <v>1156.83</v>
       </c>
       <c r="H27" s="9">
@@ -3444,7 +3449,7 @@
         <v/>
       </c>
       <c r="L27" s="9">
-        <f>G27*GP_Phil_Pct</f>
+        <f>G27*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M27" s="9">
@@ -3476,7 +3481,7 @@
       <c r="F28" s="9" t="n">
         <v>3826.11</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="10" t="n">
         <v>1147.83</v>
       </c>
       <c r="H28" s="9">
@@ -3496,7 +3501,7 @@
         <v/>
       </c>
       <c r="L28" s="9">
-        <f>G28*GP_Phil_Pct</f>
+        <f>G28*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M28" s="9">
@@ -3528,7 +3533,7 @@
       <c r="F29" s="9" t="n">
         <v>3805.49</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="10" t="n">
         <v>1141.65</v>
       </c>
       <c r="H29" s="9">
@@ -3548,7 +3553,7 @@
         <v/>
       </c>
       <c r="L29" s="9">
-        <f>G29*GP_Phil_Pct</f>
+        <f>G29*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M29" s="9">
@@ -3580,7 +3585,7 @@
       <c r="F30" s="9" t="n">
         <v>3805.49</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="10" t="n">
         <v>1141.65</v>
       </c>
       <c r="H30" s="9">
@@ -3600,7 +3605,7 @@
         <v/>
       </c>
       <c r="L30" s="9">
-        <f>G30*GP_Phil_Pct</f>
+        <f>G30*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M30" s="9">
@@ -3632,7 +3637,7 @@
       <c r="F31" s="9" t="n">
         <v>3773.18</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="10" t="n">
         <v>1131.95</v>
       </c>
       <c r="H31" s="9">
@@ -3652,7 +3657,7 @@
         <v/>
       </c>
       <c r="L31" s="9">
-        <f>G31*GP_Phil_Pct</f>
+        <f>G31*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M31" s="9">
@@ -3684,7 +3689,7 @@
       <c r="F32" s="9" t="n">
         <v>3773.12</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="10" t="n">
         <v>1131.94</v>
       </c>
       <c r="H32" s="9">
@@ -3704,7 +3709,7 @@
         <v/>
       </c>
       <c r="L32" s="9">
-        <f>G32*GP_Phil_Pct</f>
+        <f>G32*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M32" s="9">
@@ -3736,7 +3741,7 @@
       <c r="F33" s="9" t="n">
         <v>3741.67</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G33" s="10" t="n">
         <v>1122.5</v>
       </c>
       <c r="H33" s="9">
@@ -3756,7 +3761,7 @@
         <v/>
       </c>
       <c r="L33" s="9">
-        <f>G33*GP_Phil_Pct</f>
+        <f>G33*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M33" s="9">
@@ -3788,7 +3793,7 @@
       <c r="F34" s="9" t="n">
         <v>3741.67</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G34" s="10" t="n">
         <v>1122.5</v>
       </c>
       <c r="H34" s="9">
@@ -3808,7 +3813,7 @@
         <v/>
       </c>
       <c r="L34" s="9">
-        <f>G34*GP_Phil_Pct</f>
+        <f>G34*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M34" s="9">
@@ -3840,7 +3845,7 @@
       <c r="F35" s="9" t="n">
         <v>3682.02</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G35" s="10" t="n">
         <v>1104.61</v>
       </c>
       <c r="H35" s="9">
@@ -3860,7 +3865,7 @@
         <v/>
       </c>
       <c r="L35" s="9">
-        <f>G35*GP_Phil_Pct</f>
+        <f>G35*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M35" s="9">
@@ -3892,7 +3897,7 @@
       <c r="F36" s="9" t="n">
         <v>3666</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="10" t="n">
         <v>1099.8</v>
       </c>
       <c r="H36" s="9">
@@ -3912,7 +3917,7 @@
         <v/>
       </c>
       <c r="L36" s="9">
-        <f>G36*GP_Phil_Pct</f>
+        <f>G36*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M36" s="9">
@@ -3944,7 +3949,7 @@
       <c r="F37" s="9" t="n">
         <v>3664.33</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="G37" s="10" t="n">
         <v>1099.3</v>
       </c>
       <c r="H37" s="9">
@@ -3964,7 +3969,7 @@
         <v/>
       </c>
       <c r="L37" s="9">
-        <f>G37*GP_Phil_Pct</f>
+        <f>G37*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M37" s="9">
@@ -3996,7 +4001,7 @@
       <c r="F38" s="9" t="n">
         <v>3664.33</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="G38" s="10" t="n">
         <v>1099.3</v>
       </c>
       <c r="H38" s="9">
@@ -4016,7 +4021,7 @@
         <v/>
       </c>
       <c r="L38" s="9">
-        <f>G38*GP_Phil_Pct</f>
+        <f>G38*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M38" s="9">
@@ -4048,7 +4053,7 @@
       <c r="F39" s="9" t="n">
         <v>3645.58</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="10" t="n">
         <v>1093.67</v>
       </c>
       <c r="H39" s="9">
@@ -4068,7 +4073,7 @@
         <v/>
       </c>
       <c r="L39" s="9">
-        <f>G39*GP_Phil_Pct</f>
+        <f>G39*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M39" s="9">
@@ -4100,7 +4105,7 @@
       <c r="F40" s="9" t="n">
         <v>3509.75</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="10" t="n">
         <v>1052.92</v>
       </c>
       <c r="H40" s="9">
@@ -4120,7 +4125,7 @@
         <v/>
       </c>
       <c r="L40" s="9">
-        <f>G40*GP_Phil_Pct</f>
+        <f>G40*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M40" s="9">
@@ -4152,7 +4157,7 @@
       <c r="F41" s="9" t="n">
         <v>3474.88</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="G41" s="10" t="n">
         <v>1042.46</v>
       </c>
       <c r="H41" s="9">
@@ -4172,7 +4177,7 @@
         <v/>
       </c>
       <c r="L41" s="9">
-        <f>G41*GP_Phil_Pct</f>
+        <f>G41*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M41" s="9">
@@ -4204,7 +4209,7 @@
       <c r="F42" s="9" t="n">
         <v>3473.17</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="G42" s="10" t="n">
         <v>1041.95</v>
       </c>
       <c r="H42" s="9">
@@ -4224,7 +4229,7 @@
         <v/>
       </c>
       <c r="L42" s="9">
-        <f>G42*GP_Phil_Pct</f>
+        <f>G42*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M42" s="9">
@@ -4256,7 +4261,7 @@
       <c r="F43" s="9" t="n">
         <v>3472.55</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="10" t="n">
         <v>1041.76</v>
       </c>
       <c r="H43" s="9">
@@ -4276,7 +4281,7 @@
         <v/>
       </c>
       <c r="L43" s="9">
-        <f>G43*GP_Phil_Pct</f>
+        <f>G43*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M43" s="9">
@@ -4308,7 +4313,7 @@
       <c r="F44" s="9" t="n">
         <v>3438.79</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="10" t="n">
         <v>1031.64</v>
       </c>
       <c r="H44" s="9">
@@ -4328,7 +4333,7 @@
         <v/>
       </c>
       <c r="L44" s="9">
-        <f>G44*GP_Phil_Pct</f>
+        <f>G44*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M44" s="9">
@@ -4360,7 +4365,7 @@
       <c r="F45" s="9" t="n">
         <v>3438.79</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="10" t="n">
         <v>1031.64</v>
       </c>
       <c r="H45" s="9">
@@ -4380,7 +4385,7 @@
         <v/>
       </c>
       <c r="L45" s="9">
-        <f>G45*GP_Phil_Pct</f>
+        <f>G45*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M45" s="9">
@@ -4412,7 +4417,7 @@
       <c r="F46" s="9" t="n">
         <v>2709.62</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="10" t="n">
         <v>812.88</v>
       </c>
       <c r="H46" s="9">
@@ -4432,7 +4437,7 @@
         <v/>
       </c>
       <c r="L46" s="9">
-        <f>G46*GP_Phil_Pct</f>
+        <f>G46*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M46" s="9">
@@ -4464,7 +4469,7 @@
       <c r="F47" s="9" t="n">
         <v>2630.01</v>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="10" t="n">
         <v>789</v>
       </c>
       <c r="H47" s="9">
@@ -4484,7 +4489,7 @@
         <v/>
       </c>
       <c r="L47" s="9">
-        <f>G47*GP_Phil_Pct</f>
+        <f>G47*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M47" s="9">
@@ -4516,7 +4521,7 @@
       <c r="F48" s="9" t="n">
         <v>2159.37</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" s="10" t="n">
         <v>647.8099999999999</v>
       </c>
       <c r="H48" s="9">
@@ -4536,7 +4541,7 @@
         <v/>
       </c>
       <c r="L48" s="9">
-        <f>G48*GP_Phil_Pct</f>
+        <f>G48*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M48" s="9">
@@ -4568,7 +4573,7 @@
       <c r="F49" s="9" t="n">
         <v>1916.26</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G49" s="10" t="n">
         <v>574.88</v>
       </c>
       <c r="H49" s="9">
@@ -4588,7 +4593,7 @@
         <v/>
       </c>
       <c r="L49" s="9">
-        <f>G49*GP_Phil_Pct</f>
+        <f>G49*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M49" s="9">
@@ -4620,7 +4625,7 @@
       <c r="F50" s="9" t="n">
         <v>1381.34</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" s="10" t="n">
         <v>414.4</v>
       </c>
       <c r="H50" s="9">
@@ -4640,7 +4645,7 @@
         <v/>
       </c>
       <c r="L50" s="9">
-        <f>G50*GP_Phil_Pct</f>
+        <f>G50*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M50" s="9">
@@ -4672,7 +4677,7 @@
       <c r="F51" s="9" t="n">
         <v>36.96</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G51" s="10" t="n">
         <v>11.09</v>
       </c>
       <c r="H51" s="9">
@@ -4692,7 +4697,7 @@
         <v/>
       </c>
       <c r="L51" s="9">
-        <f>G51*GP_Phil_Pct</f>
+        <f>G51*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M51" s="9">
@@ -4724,7 +4729,7 @@
       <c r="F52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="9">
@@ -4744,7 +4749,7 @@
         <v/>
       </c>
       <c r="L52" s="9">
-        <f>G52*GP_Phil_Pct</f>
+        <f>G52*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M52" s="9">
@@ -4753,44 +4758,44 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="12">
         <f>SUM(D2:D52)</f>
         <v/>
       </c>
-      <c r="E53" s="11">
+      <c r="E53" s="12">
         <f>SUM(E2:E52)</f>
         <v/>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="12">
         <f>SUM(F2:F52)</f>
         <v/>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="12">
         <f>SUM(G2:G52)</f>
         <v/>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="12">
         <f>SUM(H2:H52)</f>
         <v/>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="12">
         <f>SUM(I2:I52)</f>
         <v/>
       </c>
-      <c r="J53" s="11">
+      <c r="J53" s="12">
         <f>SUM(J2:J52)</f>
         <v/>
       </c>
-      <c r="K53" s="11">
+      <c r="K53" s="12">
         <f>SUM(K2:K52)</f>
         <v/>
       </c>
-      <c r="L53" s="11">
+      <c r="L53" s="12">
         <f>SUM(L2:L52)</f>
         <v/>
       </c>
@@ -4877,7 +4882,7 @@
         <f>SUMIF(PI_Consultant, A2, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="13">
         <f>IFERROR(D2/$D$11,0)</f>
         <v/>
       </c>
@@ -4908,7 +4913,7 @@
         <f>SUMIF(PI_Consultant, A3, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <f>IFERROR(D3/$D$11,0)</f>
         <v/>
       </c>
@@ -4939,7 +4944,7 @@
         <f>SUMIF(PI_Consultant, A4, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <f>IFERROR(D4/$D$11,0)</f>
         <v/>
       </c>
@@ -4970,7 +4975,7 @@
         <f>SUMIF(PI_Consultant, A5, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <f>IFERROR(D5/$D$11,0)</f>
         <v/>
       </c>
@@ -5001,7 +5006,7 @@
         <f>SUMIF(PI_Consultant, A6, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <f>IFERROR(D6/$D$11,0)</f>
         <v/>
       </c>
@@ -5015,7 +5020,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Fund Mgmt</t>
         </is>
@@ -5032,7 +5037,7 @@
         <f>SUM(PI_FundMgmt)</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <f>IFERROR(D7/$D$11,0)</f>
         <v/>
       </c>
@@ -5046,7 +5051,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Raj (fixed 0.5%)</t>
         </is>
@@ -5065,7 +5070,7 @@
         <f>SUM(PI_PerfFee)*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>IFERROR(D8/$D$11,0)</f>
         <v/>
       </c>
@@ -5079,7 +5084,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Nairne (fixed 0.5%)</t>
         </is>
@@ -5098,7 +5103,7 @@
         <f>SUM(PI_PerfFee)*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <f>IFERROR(D9/$D$11,0)</f>
         <v/>
       </c>
@@ -5112,9 +5117,9 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Phil (fixed 0.5%)</t>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5128,10 +5133,10 @@
         </is>
       </c>
       <c r="D10" s="9">
-        <f>SUM(PI_PerfFee)*GP_Phil_Pct</f>
-        <v/>
-      </c>
-      <c r="E10" s="12">
+        <f>SUM(PI_PerfFee)*GP_Alec_Pct</f>
+        <v/>
+      </c>
+      <c r="E10" s="13">
         <f>IFERROR(D10/$D$11,0)</f>
         <v/>
       </c>
@@ -5145,20 +5150,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>GP POOL TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="12">
         <f>SUM(D2:D10)</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <f>SUM(F2:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="12">
         <f>SUM(G2:G10)</f>
         <v/>
       </c>
@@ -5169,6 +5174,366 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Operating Costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Period: Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>% of Pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D5" s="13">
+        <f>B5/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="13">
+        <f>B6/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chris (Hotel+Ticket)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>3226.17</v>
+      </c>
+      <c r="D7" s="13">
+        <f>B7/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Charalece</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D8" s="13">
+        <f>B8/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alec (Ticket)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>886</v>
+      </c>
+      <c r="D9" s="13">
+        <f>B9/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alec (Hotel)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D10" s="13">
+        <f>B10/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>6750</v>
+      </c>
+      <c r="D11" s="13">
+        <f>B11/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>26000</v>
+      </c>
+      <c r="D12" s="13">
+        <f>B12/Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>SUM(B5:B12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
+        <f>SUM(D5:D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Allocation by GP %</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Party</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>% of GP Pool</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Allocated Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B17" s="13">
+        <f>IFERROR(VLOOKUP(A17,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="9">
+        <f>B17*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>IFERROR(VLOOKUP(A18,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="9">
+        <f>B18*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fund Hub SPV (Pending Split)</t>
+        </is>
+      </c>
+      <c r="B19" s="13">
+        <f>IFERROR(VLOOKUP(A19,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C19" s="9">
+        <f>B19*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B20" s="13">
+        <f>IFERROR(VLOOKUP(A20,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="9">
+        <f>B20*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>IFERROR(VLOOKUP(A21,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="9">
+        <f>B21*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fund Mgmt</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>IFERROR(VLOOKUP(A22,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="9">
+        <f>B22*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Raj (fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B23" s="13">
+        <f>IFERROR(VLOOKUP(A23,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="9">
+        <f>B23*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Nairne (fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B24" s="13">
+        <f>IFERROR(VLOOKUP(A24,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="9">
+        <f>B24*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B25" s="13">
+        <f>IFERROR(VLOOKUP(A25,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="9">
+        <f>B25*Costs_Total</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B26" s="16">
+        <f>SUM(B17:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="12">
+        <f>SUM(C17:C25)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5190,17 +5555,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>

--- a/Armada_Consultant_Splits.xlsx
+++ b/Armada_Consultant_Splits.xlsx
@@ -39,7 +39,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +71,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00a78bfa"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0093c5fd"/>
     </font>
     <font>
       <i val="1"/>
@@ -130,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,8 +158,11 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2025,7 +2036,7 @@
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -2116,9 +2127,10 @@
           <t>Philip Okala</t>
         </is>
       </c>
-      <c r="C2">
-        <f>IFERROR(XLOOKUP(A2, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D2" s="9" t="n">
         <v>0</v>
@@ -2168,9 +2180,10 @@
           <t>NC Opportunity Fund, LP</t>
         </is>
       </c>
-      <c r="C3">
-        <f>IFERROR(XLOOKUP(A3, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D3" s="9" t="n">
         <v>0</v>
@@ -2220,9 +2233,10 @@
           <t>Fund Hub Investments LLC</t>
         </is>
       </c>
-      <c r="C4">
-        <f>IFERROR(XLOOKUP(A4, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fund Hub SPV (Pending Split)</t>
+        </is>
       </c>
       <c r="D4" s="9" t="n">
         <v>0</v>
@@ -2272,9 +2286,10 @@
           <t>DW MILLER LAND AND LIVESTOCK LLC</t>
         </is>
       </c>
-      <c r="C5">
-        <f>IFERROR(XLOOKUP(A5, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D5" s="9" t="n">
         <v>0</v>
@@ -2324,9 +2339,10 @@
           <t>David Loeffler and Lisa C. Loeffler</t>
         </is>
       </c>
-      <c r="C6">
-        <f>IFERROR(XLOOKUP(A6, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D6" s="9" t="n">
         <v>0</v>
@@ -2376,9 +2392,10 @@
           <t>PHF 2008 Descendants Separate Trust</t>
         </is>
       </c>
-      <c r="C7">
-        <f>IFERROR(XLOOKUP(A7, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D7" s="9" t="n">
         <v>0</v>
@@ -2428,9 +2445,10 @@
           <t>Erik Simpson</t>
         </is>
       </c>
-      <c r="C8">
-        <f>IFERROR(XLOOKUP(A8, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
       </c>
       <c r="D8" s="9" t="n">
         <v>0</v>
@@ -2480,9 +2498,10 @@
           <t>SHIRE HOLDINGS FAMILY LP</t>
         </is>
       </c>
-      <c r="C9">
-        <f>IFERROR(XLOOKUP(A9, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D9" s="9" t="n">
         <v>0</v>
@@ -2532,9 +2551,10 @@
           <t>Steve Corpuz</t>
         </is>
       </c>
-      <c r="C10">
-        <f>IFERROR(XLOOKUP(A10, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D10" s="9" t="n">
         <v>0</v>
@@ -2584,9 +2604,10 @@
           <t>Reid Sessions</t>
         </is>
       </c>
-      <c r="C11">
-        <f>IFERROR(XLOOKUP(A11, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D11" s="9" t="n">
         <v>0</v>
@@ -2636,9 +2657,10 @@
           <t>Doug Corpuz</t>
         </is>
       </c>
-      <c r="C12">
-        <f>IFERROR(XLOOKUP(A12, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D12" s="9" t="n">
         <v>0</v>
@@ -2688,9 +2710,10 @@
           <t>AltoIRA Custodian FBO Michelle Henriques</t>
         </is>
       </c>
-      <c r="C13">
-        <f>IFERROR(XLOOKUP(A13, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D13" s="9" t="n">
         <v>0</v>
@@ -2740,9 +2763,10 @@
           <t>Colin Steinberg</t>
         </is>
       </c>
-      <c r="C14">
-        <f>IFERROR(XLOOKUP(A14, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D14" s="9" t="n">
         <v>0</v>
@@ -2792,9 +2816,10 @@
           <t>Philippe Henriques</t>
         </is>
       </c>
-      <c r="C15">
-        <f>IFERROR(XLOOKUP(A15, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D15" s="9" t="n">
         <v>0</v>
@@ -2844,9 +2869,10 @@
           <t>Benjamin Smith</t>
         </is>
       </c>
-      <c r="C16">
-        <f>IFERROR(XLOOKUP(A16, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D16" s="9" t="n">
         <v>0</v>
@@ -2896,9 +2922,10 @@
           <t>Yan Purba</t>
         </is>
       </c>
-      <c r="C17">
-        <f>IFERROR(XLOOKUP(A17, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
@@ -2948,9 +2975,10 @@
           <t>AltoIRA Custodian FBO Marcus Whitney</t>
         </is>
       </c>
-      <c r="C18">
-        <f>IFERROR(XLOOKUP(A18, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D18" s="9" t="n">
         <v>0</v>
@@ -3000,9 +3028,10 @@
           <t>PGJCHoldings LLC</t>
         </is>
       </c>
-      <c r="C19">
-        <f>IFERROR(XLOOKUP(A19, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D19" s="9" t="n">
         <v>0</v>
@@ -3052,9 +3081,10 @@
           <t>Douglas Wilcox and Miles Wesley Wilcox</t>
         </is>
       </c>
-      <c r="C20">
-        <f>IFERROR(XLOOKUP(A20, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
@@ -3104,9 +3134,10 @@
           <t>Platte River Holdings LLC</t>
         </is>
       </c>
-      <c r="C21">
-        <f>IFERROR(XLOOKUP(A21, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D21" s="9" t="n">
         <v>0</v>
@@ -3156,9 +3187,10 @@
           <t>Joshua W Miller and Brooke G Miller</t>
         </is>
       </c>
-      <c r="C22">
-        <f>IFERROR(XLOOKUP(A22, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D22" s="9" t="n">
         <v>0</v>
@@ -3208,9 +3240,10 @@
           <t>Fred Gorges</t>
         </is>
       </c>
-      <c r="C23">
-        <f>IFERROR(XLOOKUP(A23, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
@@ -3260,9 +3293,10 @@
           <t>Bryce Dee Christensen</t>
         </is>
       </c>
-      <c r="C24">
-        <f>IFERROR(XLOOKUP(A24, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
@@ -3312,9 +3346,10 @@
           <t>David Anderson</t>
         </is>
       </c>
-      <c r="C25">
-        <f>IFERROR(XLOOKUP(A25, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D25" s="9" t="n">
         <v>0</v>
@@ -3364,9 +3399,10 @@
           <t>Madison Trust Company, Custodian FBO David Gordon Affleck M24122132</t>
         </is>
       </c>
-      <c r="C26">
-        <f>IFERROR(XLOOKUP(A26, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
       </c>
       <c r="D26" s="9" t="n">
         <v>0</v>
@@ -3416,9 +3452,10 @@
           <t>BENIK LLC</t>
         </is>
       </c>
-      <c r="C27">
-        <f>IFERROR(XLOOKUP(A27, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D27" s="9" t="n">
         <v>0</v>
@@ -3468,9 +3505,10 @@
           <t>John Hudson Taylor Anderson</t>
         </is>
       </c>
-      <c r="C28">
-        <f>IFERROR(XLOOKUP(A28, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D28" s="9" t="n">
         <v>0</v>
@@ -3520,9 +3558,10 @@
           <t>Jerry Dwayne Fussell</t>
         </is>
       </c>
-      <c r="C29">
-        <f>IFERROR(XLOOKUP(A29, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D29" s="9" t="n">
         <v>0</v>
@@ -3572,9 +3611,10 @@
           <t>Ten Eighty Trading LLC</t>
         </is>
       </c>
-      <c r="C30">
-        <f>IFERROR(XLOOKUP(A30, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D30" s="9" t="n">
         <v>0</v>
@@ -3624,9 +3664,10 @@
           <t>Caleb Andrew Cupp</t>
         </is>
       </c>
-      <c r="C31">
-        <f>IFERROR(XLOOKUP(A31, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D31" s="9" t="n">
         <v>0</v>
@@ -3676,9 +3717,10 @@
           <t>Scott Gordon and Tiffany Dyer Gordon</t>
         </is>
       </c>
-      <c r="C32">
-        <f>IFERROR(XLOOKUP(A32, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D32" s="9" t="n">
         <v>0</v>
@@ -3728,9 +3770,10 @@
           <t>MATTHEW AND MELINDA WILLIAMS CHARITABLE REMAINDER UNITRUST</t>
         </is>
       </c>
-      <c r="C33">
-        <f>IFERROR(XLOOKUP(A33, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D33" s="9" t="n">
         <v>0</v>
@@ -3780,9 +3823,10 @@
           <t>Sean D. Reyes</t>
         </is>
       </c>
-      <c r="C34">
-        <f>IFERROR(XLOOKUP(A34, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D34" s="9" t="n">
         <v>0</v>
@@ -3832,9 +3876,10 @@
           <t>PL Investment Group, LLC</t>
         </is>
       </c>
-      <c r="C35">
-        <f>IFERROR(XLOOKUP(A35, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D35" s="9" t="n">
         <v>0</v>
@@ -3884,9 +3929,10 @@
           <t>Craig Levinson</t>
         </is>
       </c>
-      <c r="C36">
-        <f>IFERROR(XLOOKUP(A36, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
       </c>
       <c r="D36" s="9" t="n">
         <v>0</v>
@@ -3936,9 +3982,10 @@
           <t>Daniel Welch Kirkham</t>
         </is>
       </c>
-      <c r="C37">
-        <f>IFERROR(XLOOKUP(A37, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
       </c>
       <c r="D37" s="9" t="n">
         <v>0</v>
@@ -3988,9 +4035,10 @@
           <t>John Charles Kirkham</t>
         </is>
       </c>
-      <c r="C38">
-        <f>IFERROR(XLOOKUP(A38, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
       </c>
       <c r="D38" s="9" t="n">
         <v>0</v>
@@ -4040,9 +4088,10 @@
           <t>Advanta Trust Company Inc. FBO Shreekanth Karwande IRA 1522282</t>
         </is>
       </c>
-      <c r="C39">
-        <f>IFERROR(XLOOKUP(A39, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
       </c>
       <c r="D39" s="9" t="n">
         <v>0</v>
@@ -4092,9 +4141,10 @@
           <t>James Lockhart</t>
         </is>
       </c>
-      <c r="C40">
-        <f>IFERROR(XLOOKUP(A40, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D40" s="9" t="n">
         <v>0</v>
@@ -4144,9 +4194,10 @@
           <t>Lyman Phillips</t>
         </is>
       </c>
-      <c r="C41">
-        <f>IFERROR(XLOOKUP(A41, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D41" s="9" t="n">
         <v>0</v>
@@ -4196,9 +4247,10 @@
           <t>Lori Brennan</t>
         </is>
       </c>
-      <c r="C42">
-        <f>IFERROR(XLOOKUP(A42, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D42" s="9" t="n">
         <v>0</v>
@@ -4248,9 +4300,10 @@
           <t>Brandy and Adam Fisher</t>
         </is>
       </c>
-      <c r="C43">
-        <f>IFERROR(XLOOKUP(A43, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D43" s="9" t="n">
         <v>0</v>
@@ -4300,9 +4353,10 @@
           <t>Mashirito LLC</t>
         </is>
       </c>
-      <c r="C44">
-        <f>IFERROR(XLOOKUP(A44, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D44" s="9" t="n">
         <v>0</v>
@@ -4352,9 +4406,10 @@
           <t>Weston Shea Christensen</t>
         </is>
       </c>
-      <c r="C45">
-        <f>IFERROR(XLOOKUP(A45, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D45" s="9" t="n">
         <v>0</v>
@@ -4404,9 +4459,10 @@
           <t>Frieda Goldsmith 1998 Trust</t>
         </is>
       </c>
-      <c r="C46">
-        <f>IFERROR(XLOOKUP(A46, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D46" s="9" t="n">
         <v>0</v>
@@ -4456,9 +4512,10 @@
           <t>Richard Gordon</t>
         </is>
       </c>
-      <c r="C47">
-        <f>IFERROR(XLOOKUP(A47, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D47" s="9" t="n">
         <v>0</v>
@@ -4508,9 +4565,10 @@
           <t>Golden Touch Properties LLC</t>
         </is>
       </c>
-      <c r="C48">
-        <f>IFERROR(XLOOKUP(A48, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
       </c>
       <c r="D48" s="9" t="n">
         <v>0</v>
@@ -4560,9 +4618,10 @@
           <t>Treyson Gordon</t>
         </is>
       </c>
-      <c r="C49">
-        <f>IFERROR(XLOOKUP(A49, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
       </c>
       <c r="D49" s="9" t="n">
         <v>0</v>
@@ -4612,9 +4671,10 @@
           <t>The Atkinson Group LLC</t>
         </is>
       </c>
-      <c r="C50">
-        <f>IFERROR(XLOOKUP(A50, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D50" s="9" t="n">
         <v>0</v>
@@ -4664,9 +4724,10 @@
           <t>Mitchell Squires</t>
         </is>
       </c>
-      <c r="C51">
-        <f>IFERROR(XLOOKUP(A51, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D51" s="9" t="n">
         <v>0</v>
@@ -4716,9 +4777,10 @@
           <t>Joel Guy and Jennifer Pasetes</t>
         </is>
       </c>
-      <c r="C52">
-        <f>IFERROR(XLOOKUP(A52, IDS_TPA, IDS_Consultant), "Unmapped")</f>
-        <v/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
       </c>
       <c r="D52" s="9" t="n">
         <v>0</v>
@@ -4815,7 +4877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4824,7 +4886,7 @@
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4845,7 +4907,7 @@
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>GP Earned</t>
+          <t>Gross GP</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
@@ -4855,12 +4917,12 @@
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>Allocated Expenses</t>
+          <t>Weighted Expense</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>Net Payout</t>
+          <t>Net Profit</t>
         </is>
       </c>
     </row>
@@ -4883,11 +4945,11 @@
         <v/>
       </c>
       <c r="E2" s="13">
-        <f>IFERROR(D2/$D$11,0)</f>
+        <f>IFERROR(D2/$D$14,0)</f>
         <v/>
       </c>
       <c r="F2" s="9">
-        <f>IFERROR(D2/$D$11,0)*Expense_Pool</f>
+        <f>IFERROR(D2/$D$14,0)*Expense_Pool</f>
         <v/>
       </c>
       <c r="G2" s="9">
@@ -4914,11 +4976,11 @@
         <v/>
       </c>
       <c r="E3" s="13">
-        <f>IFERROR(D3/$D$11,0)</f>
+        <f>IFERROR(D3/$D$14,0)</f>
         <v/>
       </c>
       <c r="F3" s="9">
-        <f>IFERROR(D3/$D$11,0)*Expense_Pool</f>
+        <f>IFERROR(D3/$D$14,0)*Expense_Pool</f>
         <v/>
       </c>
       <c r="G3" s="9">
@@ -4945,11 +5007,11 @@
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>IFERROR(D4/$D$11,0)</f>
+        <f>IFERROR(D4/$D$14,0)</f>
         <v/>
       </c>
       <c r="F4" s="9">
-        <f>IFERROR(D4/$D$11,0)*Expense_Pool</f>
+        <f>IFERROR(D4/$D$14,0)*Expense_Pool</f>
         <v/>
       </c>
       <c r="G4" s="9">
@@ -4976,11 +5038,11 @@
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>IFERROR(D5/$D$11,0)</f>
+        <f>IFERROR(D5/$D$14,0)</f>
         <v/>
       </c>
       <c r="F5" s="9">
-        <f>IFERROR(D5/$D$11,0)*Expense_Pool</f>
+        <f>IFERROR(D5/$D$14,0)*Expense_Pool</f>
         <v/>
       </c>
       <c r="G5" s="9">
@@ -5007,11 +5069,11 @@
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>IFERROR(D6/$D$11,0)</f>
+        <f>IFERROR(D6/$D$14,0)</f>
         <v/>
       </c>
       <c r="F6" s="9">
-        <f>IFERROR(D6/$D$11,0)*Expense_Pool</f>
+        <f>IFERROR(D6/$D$14,0)*Expense_Pool</f>
         <v/>
       </c>
       <c r="G6" s="9">
@@ -5022,126 +5084,68 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
+          <t>CONSULTANTS SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B7" s="15">
+        <f>SUM(B2:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>SUM(C2:C6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="12">
+        <f>SUM(D2:D6)</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>IFERROR(D7/$D$14,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>SUM(F2:F6)</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>SUM(G2:G6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>GP POOL — OTHER RECIPIENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
           <t>Fund Mgmt</t>
         </is>
       </c>
-      <c r="B7">
-        <f>COUNTA(PI_Consultant)</f>
-        <v/>
-      </c>
-      <c r="C7" s="9">
-        <f>SUM(PI_Capital)</f>
-        <v/>
-      </c>
-      <c r="D7" s="9">
-        <f>SUM(PI_FundMgmt)</f>
-        <v/>
-      </c>
-      <c r="E7" s="13">
-        <f>IFERROR(D7/$D$11,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="9">
-        <f>IFERROR(D7/$D$11,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G7" s="9">
-        <f>D7-F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Raj (fixed 0.5%)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="9">
-        <f>SUM(PI_PerfFee)*GP_Raj_Pct</f>
-        <v/>
-      </c>
-      <c r="E8" s="13">
-        <f>IFERROR(D8/$D$11,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="9">
-        <f>IFERROR(D8/$D$11,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G8" s="9">
-        <f>D8-F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Nairne (fixed 0.5%)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="9">
-        <f>SUM(PI_PerfFee)*GP_Nairne_Pct</f>
-        <v/>
-      </c>
-      <c r="E9" s="13">
-        <f>IFERROR(D9/$D$11,0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="9">
-        <f>IFERROR(D9/$D$11,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G9" s="9">
-        <f>D9-F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Alec (GP fixed 0.5%)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D10" s="9">
-        <f>SUM(PI_PerfFee)*GP_Alec_Pct</f>
+        <f>SUM(PI_PerfFee)*GP_FundMgmt_Pct</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>IFERROR(D10/$D$11,0)</f>
+        <f>IFERROR(D10/$D$14,0)</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IFERROR(D10/$D$11,0)*Expense_Pool</f>
+        <f>IFERROR(D10/$D$14,0)*Expense_Pool</f>
         <v/>
       </c>
       <c r="G10" s="9">
@@ -5150,21 +5154,126 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Raj (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="9">
+        <f>SUM(PI_PerfFee)*GP_Raj_Pct</f>
+        <v/>
+      </c>
+      <c r="E11" s="13">
+        <f>IFERROR(D11/$D$14,0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="9">
+        <f>IFERROR(D11/$D$14,0)*Expense_Pool</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>D11-F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>Nairne (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="9">
+        <f>SUM(PI_PerfFee)*GP_Nairne_Pct</f>
+        <v/>
+      </c>
+      <c r="E12" s="13">
+        <f>IFERROR(D12/$D$14,0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>IFERROR(D12/$D$14,0)*Expense_Pool</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>D12-F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="9">
+        <f>SUM(PI_PerfFee)*GP_Alec_Pct</f>
+        <v/>
+      </c>
+      <c r="E13" s="13">
+        <f>IFERROR(D13/$D$14,0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="9">
+        <f>IFERROR(D13/$D$14,0)*Expense_Pool</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>D13-F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>GP POOL TOTAL</t>
         </is>
       </c>
-      <c r="D11" s="12">
-        <f>SUM(D2:D10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>SUM(F2:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="12">
-        <f>SUM(G2:G10)</f>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="12">
+        <f>SUM(D2:D6)+SUM(D10:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>D14/$D$14</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>Expense_Pool</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>D14-F14</f>
         <v/>
       </c>
     </row>
@@ -5382,7 +5491,7 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>IFERROR(VLOOKUP(A17,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A17,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C17" s="9">
@@ -5397,7 +5506,7 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>IFERROR(VLOOKUP(A18,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A18,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C18" s="9">
@@ -5412,7 +5521,7 @@
         </is>
       </c>
       <c r="B19" s="13">
-        <f>IFERROR(VLOOKUP(A19,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A19,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C19" s="9">
@@ -5427,7 +5536,7 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>IFERROR(VLOOKUP(A20,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A20,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C20" s="9">
@@ -5442,7 +5551,7 @@
         </is>
       </c>
       <c r="B21" s="13">
-        <f>IFERROR(VLOOKUP(A21,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A21,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C21" s="9">
@@ -5457,7 +5566,7 @@
         </is>
       </c>
       <c r="B22" s="13">
-        <f>IFERROR(VLOOKUP(A22,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A22,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C22" s="9">
@@ -5468,11 +5577,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raj (fixed 0.5%)</t>
+          <t>Raj (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B23" s="13">
-        <f>IFERROR(VLOOKUP(A23,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A23,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C23" s="9">
@@ -5483,11 +5592,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nairne (fixed 0.5%)</t>
+          <t>Nairne (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B24" s="13">
-        <f>IFERROR(VLOOKUP(A24,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A24,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C24" s="9">
@@ -5502,7 +5611,7 @@
         </is>
       </c>
       <c r="B25" s="13">
-        <f>IFERROR(VLOOKUP(A25,'Consultant Summary'!$A$2:$E$10,5,FALSE),0)</f>
+        <f>IFERROR(VLOOKUP(A25,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
         <v/>
       </c>
       <c r="C25" s="9">

--- a/Armada_Consultant_Splits.xlsx
+++ b/Armada_Consultant_Splits.xlsx
@@ -21,6 +21,7 @@
     <definedName name="GP_Nairne_Pct">Inputs!$B$8</definedName>
     <definedName name="GP_Alec_Pct">Inputs!$B$9</definedName>
     <definedName name="Expense_Pool">Inputs!$B$14</definedName>
+    <definedName name="TQ_Income">Inputs!$B$17</definedName>
     <definedName name="IDS_TPA">'IDS Mapping'!$A$2:$A$52</definedName>
     <definedName name="IDS_Consultant">'IDS Mapping'!$D$2:$D$52</definedName>
     <definedName name="PI_Consultant">'Per-Investor Allocation'!$C$2:$C$52</definedName>
@@ -28,7 +29,9 @@
     <definedName name="PI_ConsultantCut">'Per-Investor Allocation'!$I$2:$I$52</definedName>
     <definedName name="PI_FundMgmt">'Per-Investor Allocation'!$H$2:$H$52</definedName>
     <definedName name="PI_Capital">'Per-Investor Allocation'!$E$2:$E$52</definedName>
-    <definedName name="Costs_Total">Costs!$B$13</definedName>
+    <definedName name="Costs_PartyHeaders">Costs!$E$5:$N$5</definedName>
+    <definedName name="Costs_PartyTotals">Costs!$E$14:$N$14</definedName>
+    <definedName name="Costs_Total">Costs!$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +42,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +90,23 @@
     <font>
       <i val="1"/>
       <color rgb="00d8b4fe"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00fbbf24"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00fbbf24"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0094a3b8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00a78bfa"/>
     </font>
   </fonts>
   <fills count="5">
@@ -138,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,6 +166,7 @@
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -153,7 +174,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +183,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -638,23 +667,40 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>TruQuant Income (upstream)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TQ takes 18% before Armada's books</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>88869.69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>TPA per-investor performance-fee crystallized = each investor's GP pool. Consultant attribution flows from IDS → Per-Investor Allocation → Consultant Summary. Edit the Per-Investor sheet to override perf_fee for what-if scenarios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>TPA per-investor performance-fee crystallized = each investor's GP pool. Consultant attribution flows from IDS → Per-Investor Allocation → Consultant Summary. Cost line items live on the Costs sheet — edit there and amounts re-flow to Consultant Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A20:F22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -677,27 +723,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>TPA ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Investor Name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Consultant</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2050,67 +2096,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>TPA ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Consultant</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Begin Balance</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Ending Balance</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Gross P&amp;L</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Perf Fee (GP Pool)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Fund Mgmt</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Consultant Cut</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Raj</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Nairne</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Alec (GP)</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Sum Check</t>
         </is>
@@ -2132,39 +2178,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="n">
+      <c r="D2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>1554446.7</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="10" t="n">
         <v>52197.71</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="7" t="n">
         <v>15659.31</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <f>G2*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <f>G2*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="10">
         <f>G2*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="10">
         <f>G2*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="10">
         <f>G2*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="10">
         <f>ROUND(SUM(H2:L2)-G2, 2)</f>
         <v/>
       </c>
@@ -2185,39 +2231,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="n">
+      <c r="D3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>1504802.83</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="10" t="n">
         <v>50530.69</v>
       </c>
-      <c r="G3" s="10" t="n">
+      <c r="G3" s="7" t="n">
         <v>15159.21</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <f>G3*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <f>G3*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="10">
         <f>G3*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="10">
         <f>G3*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="10">
         <f>G3*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="10">
         <f>ROUND(SUM(H3:L3)-G3, 2)</f>
         <v/>
       </c>
@@ -2238,39 +2284,39 @@
           <t>Fund Hub SPV (Pending Split)</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9" t="n">
+      <c r="D4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>889926.39</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>29883.38</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="7" t="n">
         <v>8965.01</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <f>G4*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <f>G4*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="10">
         <f>G4*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="10">
         <f>G4*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="10">
         <f>G4*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="10">
         <f>ROUND(SUM(H4:L4)-G4, 2)</f>
         <v/>
       </c>
@@ -2291,39 +2337,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
+      <c r="D5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>782096.09</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <v>26262.48</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="7" t="n">
         <v>7878.74</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <f>G5*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <f>G5*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="10">
         <f>G5*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="10">
         <f>G5*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="10">
         <f>G5*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="10">
         <f>ROUND(SUM(H5:L5)-G5, 2)</f>
         <v/>
       </c>
@@ -2344,39 +2390,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9" t="n">
+      <c r="D6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>736875.59</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <v>24752.48</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="7" t="n">
         <v>7425.74</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <f>G6*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <f>G6*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="10">
         <f>G6*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="10">
         <f>G6*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="10">
         <f>G6*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="10">
         <f>ROUND(SUM(H6:L6)-G6, 2)</f>
         <v/>
       </c>
@@ -2397,39 +2443,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9" t="n">
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>532695.99</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>17887.72</v>
       </c>
-      <c r="G7" s="10" t="n">
+      <c r="G7" s="7" t="n">
         <v>5366.32</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <f>G7*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="10">
         <f>G7*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="10">
         <f>G7*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="10">
         <f>G7*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="10">
         <f>G7*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="10">
         <f>ROUND(SUM(H7:L7)-G7, 2)</f>
         <v/>
       </c>
@@ -2450,39 +2496,39 @@
           <t>AJ Affleck</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9" t="n">
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>440001.9</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <v>14775.09</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="7" t="n">
         <v>4432.53</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="10">
         <f>G8*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="10">
         <f>G8*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="10">
         <f>G8*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="10">
         <f>G8*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="10">
         <f>G8*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="10">
         <f>ROUND(SUM(H8:L8)-G8, 2)</f>
         <v/>
       </c>
@@ -2503,39 +2549,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9" t="n">
+      <c r="D9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>370633.4</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <v>12445.73</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="7" t="n">
         <v>3733.72</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <f>G9*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <f>G9*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="10">
         <f>G9*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="10">
         <f>G9*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="10">
         <f>G9*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="10">
         <f>ROUND(SUM(H9:L9)-G9, 2)</f>
         <v/>
       </c>
@@ -2556,39 +2602,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9" t="n">
+      <c r="D10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>255515.88</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>8580.120000000001</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="7" t="n">
         <v>2574.04</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="10">
         <f>G10*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="10">
         <f>G10*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="10">
         <f>G10*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="10">
         <f>G10*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="10">
         <f>G10*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="10">
         <f>ROUND(SUM(H10:L10)-G10, 2)</f>
         <v/>
       </c>
@@ -2609,39 +2655,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>252800.89</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="10" t="n">
         <v>8488.959999999999</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="7" t="n">
         <v>2546.69</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="10">
         <f>G11*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="10">
         <f>G11*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="10">
         <f>G11*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="10">
         <f>G11*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="10">
         <f>G11*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="10">
         <f>ROUND(SUM(H11:L11)-G11, 2)</f>
         <v/>
       </c>
@@ -2662,39 +2708,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="D12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>206967.8</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="10" t="n">
         <v>6949.9</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="7" t="n">
         <v>2084.97</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="10">
         <f>G12*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="10">
         <f>G12*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="10">
         <f>G12*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="10">
         <f>G12*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="10">
         <f>G12*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="10">
         <f>ROUND(SUM(H12:L12)-G12, 2)</f>
         <v/>
       </c>
@@ -2715,39 +2761,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="n">
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>206861.77</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="10" t="n">
         <v>6946.34</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="7" t="n">
         <v>2083.9</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="10">
         <f>G13*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="10">
         <f>G13*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="10">
         <f>G13*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="10">
         <f>G13*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="10">
         <f>G13*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="10">
         <f>ROUND(SUM(H13:L13)-G13, 2)</f>
         <v/>
       </c>
@@ -2768,39 +2814,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
         <v>205186.49</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="10" t="n">
         <v>6890.08</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="7" t="n">
         <v>2067.02</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="10">
         <f>G14*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <f>G14*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="10">
         <f>G14*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="10">
         <f>G14*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="10">
         <f>G14*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="10">
         <f>ROUND(SUM(H14:L14)-G14, 2)</f>
         <v/>
       </c>
@@ -2821,39 +2867,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="n">
         <v>188159.19</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <v>6318.31</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="7" t="n">
         <v>1895.49</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="10">
         <f>G15*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="10">
         <f>G15*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="10">
         <f>G15*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="10">
         <f>G15*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="10">
         <f>G15*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="10">
         <f>ROUND(SUM(H15:L15)-G15, 2)</f>
         <v/>
       </c>
@@ -2874,39 +2920,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9" t="n">
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>181498.82</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="10" t="n">
         <v>6094.66</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="7" t="n">
         <v>1828.4</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="10">
         <f>G16*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="10">
         <f>G16*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="10">
         <f>G16*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="10">
         <f>G16*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="10">
         <f>G16*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="10">
         <f>ROUND(SUM(H16:L16)-G16, 2)</f>
         <v/>
       </c>
@@ -2927,39 +2973,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="9" t="n">
+      <c r="D17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="10" t="n">
         <v>167373.38</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>5620.33</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G17" s="7" t="n">
         <v>1686.1</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="10">
         <f>G17*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="10">
         <f>G17*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="10">
         <f>G17*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <f>G17*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <f>G17*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="10">
         <f>ROUND(SUM(H17:L17)-G17, 2)</f>
         <v/>
       </c>
@@ -2980,39 +3026,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="9" t="n">
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="n">
         <v>155614.84</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="10" t="n">
         <v>5225.49</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="7" t="n">
         <v>1567.65</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="10">
         <f>G18*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="10">
         <f>G18*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="10">
         <f>G18*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="10">
         <f>G18*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="10">
         <f>G18*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="10">
         <f>ROUND(SUM(H18:L18)-G18, 2)</f>
         <v/>
       </c>
@@ -3033,39 +3079,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="9" t="n">
+      <c r="D19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="n">
         <v>153610.73</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="10" t="n">
         <v>5158.19</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="7" t="n">
         <v>1547.46</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="10">
         <f>G19*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="10">
         <f>G19*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="10">
         <f>G19*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="10">
         <f>G19*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="10">
         <f>G19*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="10">
         <f>ROUND(SUM(H19:L19)-G19, 2)</f>
         <v/>
       </c>
@@ -3086,39 +3132,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="9" t="n">
+      <c r="D20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>149013.12</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="10" t="n">
         <v>5003.8</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="7" t="n">
         <v>1501.14</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="10">
         <f>G20*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="10">
         <f>G20*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="10">
         <f>G20*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="10">
         <f>G20*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="10">
         <f>G20*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="10">
         <f>ROUND(SUM(H20:L20)-G20, 2)</f>
         <v/>
       </c>
@@ -3139,39 +3185,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9" t="n">
+      <c r="D21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <v>131452.82</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="10" t="n">
         <v>4414.13</v>
       </c>
-      <c r="G21" s="10" t="n">
+      <c r="G21" s="7" t="n">
         <v>1324.24</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="10">
         <f>G21*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="10">
         <f>G21*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="10">
         <f>G21*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="10">
         <f>G21*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="10">
         <f>G21*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="10">
         <f>ROUND(SUM(H21:L21)-G21, 2)</f>
         <v/>
       </c>
@@ -3192,39 +3238,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="9" t="n">
+      <c r="D22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>124076.49</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="10" t="n">
         <v>4166.44</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="7" t="n">
         <v>1249.93</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="10">
         <f>G22*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <f>G22*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="10">
         <f>G22*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="10">
         <f>G22*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="10">
         <f>G22*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="10">
         <f>ROUND(SUM(H22:L22)-G22, 2)</f>
         <v/>
       </c>
@@ -3245,39 +3291,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>120660.73</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="10" t="n">
         <v>4051.74</v>
       </c>
-      <c r="G23" s="10" t="n">
+      <c r="G23" s="7" t="n">
         <v>1215.52</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="10">
         <f>G23*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <f>G23*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="10">
         <f>G23*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="10">
         <f>G23*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="10">
         <f>G23*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="10">
         <f>ROUND(SUM(H23:L23)-G23, 2)</f>
         <v/>
       </c>
@@ -3298,39 +3344,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
+      <c r="D24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>117281.71</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="10" t="n">
         <v>3938.27</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="7" t="n">
         <v>1181.48</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="10">
         <f>G24*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="10">
         <f>G24*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="10">
         <f>G24*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="10">
         <f>G24*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="10">
         <f>G24*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="10">
         <f>ROUND(SUM(H24:L24)-G24, 2)</f>
         <v/>
       </c>
@@ -3351,39 +3397,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9" t="n">
+      <c r="D25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="10" t="n">
         <v>117028.98</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>3929.79</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="7" t="n">
         <v>1178.94</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="10">
         <f>G25*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="10">
         <f>G25*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="10">
         <f>G25*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="10">
         <f>G25*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="10">
         <f>G25*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M25" s="9">
+      <c r="M25" s="10">
         <f>ROUND(SUM(H25:L25)-G25, 2)</f>
         <v/>
       </c>
@@ -3404,39 +3450,39 @@
           <t>AJ Affleck</t>
         </is>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9" t="n">
+      <c r="D26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="n">
         <v>115616.76</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>3882.37</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="7" t="n">
         <v>1164.71</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <f>G26*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="10">
         <f>G26*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="10">
         <f>G26*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="10">
         <f>G26*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="10">
         <f>G26*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="10">
         <f>ROUND(SUM(H26:L26)-G26, 2)</f>
         <v/>
       </c>
@@ -3457,39 +3503,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="n">
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
         <v>114834.83</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>3856.11</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="7" t="n">
         <v>1156.83</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="10">
         <f>G27*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="10">
         <f>G27*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="10">
         <f>G27*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="10">
         <f>G27*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="10">
         <f>G27*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M27" s="9">
+      <c r="M27" s="10">
         <f>ROUND(SUM(H27:L27)-G27, 2)</f>
         <v/>
       </c>
@@ -3510,39 +3556,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="9" t="n">
+      <c r="D28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="n">
         <v>113941.39</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="10" t="n">
         <v>3826.11</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="7" t="n">
         <v>1147.83</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="10">
         <f>G28*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="10">
         <f>G28*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="10">
         <f>G28*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="10">
         <f>G28*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="10">
         <f>G28*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M28" s="9">
+      <c r="M28" s="10">
         <f>ROUND(SUM(H28:L28)-G28, 2)</f>
         <v/>
       </c>
@@ -3563,39 +3609,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="9" t="n">
+      <c r="D29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="n">
         <v>113327.33</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="10" t="n">
         <v>3805.49</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="7" t="n">
         <v>1141.65</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="10">
         <f>G29*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="10">
         <f>G29*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="10">
         <f>G29*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="10">
         <f>G29*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="10">
         <f>G29*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="10">
         <f>ROUND(SUM(H29:L29)-G29, 2)</f>
         <v/>
       </c>
@@ -3616,39 +3662,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="9" t="n">
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>113327.33</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="10" t="n">
         <v>3805.49</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="7" t="n">
         <v>1141.65</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="10">
         <f>G30*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="10">
         <f>G30*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="10">
         <f>G30*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="10">
         <f>G30*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="10">
         <f>G30*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M30" s="9">
+      <c r="M30" s="10">
         <f>ROUND(SUM(H30:L30)-G30, 2)</f>
         <v/>
       </c>
@@ -3669,39 +3715,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9" t="n">
+      <c r="D31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="n">
         <v>112365.21</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>3773.18</v>
       </c>
-      <c r="G31" s="10" t="n">
+      <c r="G31" s="7" t="n">
         <v>1131.95</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="10">
         <f>G31*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="10">
         <f>G31*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="10">
         <f>G31*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="10">
         <f>G31*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="10">
         <f>G31*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M31" s="9">
+      <c r="M31" s="10">
         <f>ROUND(SUM(H31:L31)-G31, 2)</f>
         <v/>
       </c>
@@ -3722,39 +3768,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="9" t="n">
+      <c r="D32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>112363.57</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="10" t="n">
         <v>3773.12</v>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="G32" s="7" t="n">
         <v>1131.94</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="10">
         <f>G32*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="10">
         <f>G32*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="10">
         <f>G32*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="10">
         <f>G32*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="10">
         <f>G32*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M32" s="9">
+      <c r="M32" s="10">
         <f>ROUND(SUM(H32:L32)-G32, 2)</f>
         <v/>
       </c>
@@ -3775,39 +3821,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="9" t="n">
+      <c r="D33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="10" t="n">
         <v>111426.88</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="10" t="n">
         <v>3741.67</v>
       </c>
-      <c r="G33" s="10" t="n">
+      <c r="G33" s="7" t="n">
         <v>1122.5</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="10">
         <f>G33*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="10">
         <f>G33*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="10">
         <f>G33*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="10">
         <f>G33*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="10">
         <f>G33*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="10">
         <f>ROUND(SUM(H33:L33)-G33, 2)</f>
         <v/>
       </c>
@@ -3828,39 +3874,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9" t="n">
+      <c r="D34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10" t="n">
         <v>111426.88</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="10" t="n">
         <v>3741.67</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="G34" s="7" t="n">
         <v>1122.5</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="10">
         <f>G34*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="10">
         <f>G34*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="10">
         <f>G34*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="10">
         <f>G34*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="10">
         <f>G34*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="10">
         <f>ROUND(SUM(H34:L34)-G34, 2)</f>
         <v/>
       </c>
@@ -3881,39 +3927,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="10" t="n">
         <v>109650.6</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="10" t="n">
         <v>3682.02</v>
       </c>
-      <c r="G35" s="10" t="n">
+      <c r="G35" s="7" t="n">
         <v>1104.61</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="10">
         <f>G35*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="10">
         <f>G35*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="10">
         <f>G35*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="10">
         <f>G35*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="10">
         <f>G35*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M35" s="9">
+      <c r="M35" s="10">
         <f>ROUND(SUM(H35:L35)-G35, 2)</f>
         <v/>
       </c>
@@ -3934,39 +3980,39 @@
           <t>AJ Affleck</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="9" t="n">
+      <c r="D36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="10" t="n">
         <v>109173.32</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="10" t="n">
         <v>3666</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="7" t="n">
         <v>1099.8</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="10">
         <f>G36*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="10">
         <f>G36*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="10">
         <f>G36*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="10">
         <f>G36*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="10">
         <f>G36*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M36" s="9">
+      <c r="M36" s="10">
         <f>ROUND(SUM(H36:L36)-G36, 2)</f>
         <v/>
       </c>
@@ -3987,39 +4033,39 @@
           <t>Luke</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="9" t="n">
+      <c r="D37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>109123.67</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="10" t="n">
         <v>3664.33</v>
       </c>
-      <c r="G37" s="10" t="n">
+      <c r="G37" s="7" t="n">
         <v>1099.3</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="10">
         <f>G37*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="10">
         <f>G37*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="10">
         <f>G37*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="10">
         <f>G37*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="10">
         <f>G37*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="10">
         <f>ROUND(SUM(H37:L37)-G37, 2)</f>
         <v/>
       </c>
@@ -4040,39 +4086,39 @@
           <t>AJ Affleck</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>109123.67</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>3664.33</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="7" t="n">
         <v>1099.3</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="10">
         <f>G38*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="10">
         <f>G38*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="10">
         <f>G38*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="10">
         <f>G38*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="10">
         <f>G38*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M38" s="9">
+      <c r="M38" s="10">
         <f>ROUND(SUM(H38:L38)-G38, 2)</f>
         <v/>
       </c>
@@ -4093,39 +4139,39 @@
           <t>Luke</t>
         </is>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="10" t="n">
         <v>108565.29</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="10" t="n">
         <v>3645.58</v>
       </c>
-      <c r="G39" s="10" t="n">
+      <c r="G39" s="7" t="n">
         <v>1093.67</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="10">
         <f>G39*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="10">
         <f>G39*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="10">
         <f>G39*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="10">
         <f>G39*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="10">
         <f>G39*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M39" s="9">
+      <c r="M39" s="10">
         <f>ROUND(SUM(H39:L39)-G39, 2)</f>
         <v/>
       </c>
@@ -4146,39 +4192,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="9" t="n">
+      <c r="D40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10" t="n">
         <v>104520.17</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="10" t="n">
         <v>3509.75</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G40" s="7" t="n">
         <v>1052.92</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="10">
         <f>G40*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="10">
         <f>G40*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="10">
         <f>G40*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="10">
         <f>G40*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="10">
         <f>G40*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M40" s="9">
+      <c r="M40" s="10">
         <f>ROUND(SUM(H40:L40)-G40, 2)</f>
         <v/>
       </c>
@@ -4199,39 +4245,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="9" t="n">
+      <c r="D41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="10" t="n">
         <v>103481.71</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="10" t="n">
         <v>3474.88</v>
       </c>
-      <c r="G41" s="10" t="n">
+      <c r="G41" s="7" t="n">
         <v>1042.46</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="10">
         <f>G41*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="10">
         <f>G41*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="10">
         <f>G41*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="10">
         <f>G41*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="10">
         <f>G41*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M41" s="9">
+      <c r="M41" s="10">
         <f>ROUND(SUM(H41:L41)-G41, 2)</f>
         <v/>
       </c>
@@ -4252,39 +4298,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="9" t="n">
+      <c r="D42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10" t="n">
         <v>103430.88</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="10" t="n">
         <v>3473.17</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="G42" s="7" t="n">
         <v>1041.95</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="10">
         <f>G42*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="10">
         <f>G42*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="10">
         <f>G42*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="10">
         <f>G42*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="10">
         <f>G42*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="10">
         <f>ROUND(SUM(H42:L42)-G42, 2)</f>
         <v/>
       </c>
@@ -4305,39 +4351,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="9" t="n">
+      <c r="D43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="10" t="n">
         <v>103412.44</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="10" t="n">
         <v>3472.55</v>
       </c>
-      <c r="G43" s="10" t="n">
+      <c r="G43" s="7" t="n">
         <v>1041.76</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="10">
         <f>G43*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="10">
         <f>G43*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J43" s="9">
+      <c r="J43" s="10">
         <f>G43*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="10">
         <f>G43*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L43" s="9">
+      <c r="L43" s="10">
         <f>G43*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M43" s="9">
+      <c r="M43" s="10">
         <f>ROUND(SUM(H43:L43)-G43, 2)</f>
         <v/>
       </c>
@@ -4358,39 +4404,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9" t="n">
+      <c r="D44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10" t="n">
         <v>102407.15</v>
       </c>
-      <c r="F44" s="9" t="n">
+      <c r="F44" s="10" t="n">
         <v>3438.79</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="7" t="n">
         <v>1031.64</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="10">
         <f>G44*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="10">
         <f>G44*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="10">
         <f>G44*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K44" s="9">
+      <c r="K44" s="10">
         <f>G44*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L44" s="9">
+      <c r="L44" s="10">
         <f>G44*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M44" s="9">
+      <c r="M44" s="10">
         <f>ROUND(SUM(H44:L44)-G44, 2)</f>
         <v/>
       </c>
@@ -4411,39 +4457,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="9" t="n">
+      <c r="D45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="10" t="n">
         <v>102407.15</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>3438.79</v>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G45" s="7" t="n">
         <v>1031.64</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="10">
         <f>G45*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="10">
         <f>G45*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="10">
         <f>G45*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="10">
         <f>G45*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L45" s="9">
+      <c r="L45" s="10">
         <f>G45*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="10">
         <f>ROUND(SUM(H45:L45)-G45, 2)</f>
         <v/>
       </c>
@@ -4464,39 +4510,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="10" t="n">
         <v>80692.28999999999</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="10" t="n">
         <v>2709.62</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" s="7" t="n">
         <v>812.88</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="10">
         <f>G46*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="10">
         <f>G46*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="10">
         <f>G46*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="10">
         <f>G46*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L46" s="9">
+      <c r="L46" s="10">
         <f>G46*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M46" s="9">
+      <c r="M46" s="10">
         <f>ROUND(SUM(H46:L46)-G46, 2)</f>
         <v/>
       </c>
@@ -4517,39 +4563,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="9" t="n">
+      <c r="D47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="10" t="n">
         <v>78321.57000000001</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="10" t="n">
         <v>2630.01</v>
       </c>
-      <c r="G47" s="10" t="n">
+      <c r="G47" s="7" t="n">
         <v>789</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="10">
         <f>G47*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="10">
         <f>G47*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="10">
         <f>G47*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="10">
         <f>G47*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L47" s="9">
+      <c r="L47" s="10">
         <f>G47*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M47" s="9">
+      <c r="M47" s="10">
         <f>ROUND(SUM(H47:L47)-G47, 2)</f>
         <v/>
       </c>
@@ -4570,39 +4616,39 @@
           <t>AJ Affleck</t>
         </is>
       </c>
-      <c r="D48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="9" t="n">
+      <c r="D48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="10" t="n">
         <v>64305.85</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F48" s="10" t="n">
         <v>2159.37</v>
       </c>
-      <c r="G48" s="10" t="n">
+      <c r="G48" s="7" t="n">
         <v>647.8099999999999</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="10">
         <f>G48*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="10">
         <f>G48*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="10">
         <f>G48*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K48" s="9">
+      <c r="K48" s="10">
         <f>G48*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L48" s="9">
+      <c r="L48" s="10">
         <f>G48*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M48" s="9">
+      <c r="M48" s="10">
         <f>ROUND(SUM(H48:L48)-G48, 2)</f>
         <v/>
       </c>
@@ -4623,39 +4669,39 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="D49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="9" t="n">
+      <c r="D49" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="10" t="n">
         <v>57066.22</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="10" t="n">
         <v>1916.26</v>
       </c>
-      <c r="G49" s="10" t="n">
+      <c r="G49" s="7" t="n">
         <v>574.88</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="10">
         <f>G49*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="10">
         <f>G49*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="10">
         <f>G49*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="10">
         <f>G49*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L49" s="9">
+      <c r="L49" s="10">
         <f>G49*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M49" s="9">
+      <c r="M49" s="10">
         <f>ROUND(SUM(H49:L49)-G49, 2)</f>
         <v/>
       </c>
@@ -4676,39 +4722,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="9" t="n">
+      <c r="D50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="10" t="n">
         <v>41136.24</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F50" s="10" t="n">
         <v>1381.34</v>
       </c>
-      <c r="G50" s="10" t="n">
+      <c r="G50" s="7" t="n">
         <v>414.4</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="10">
         <f>G50*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="10">
         <f>G50*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="10">
         <f>G50*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K50" s="9">
+      <c r="K50" s="10">
         <f>G50*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L50" s="9">
+      <c r="L50" s="10">
         <f>G50*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="10">
         <f>ROUND(SUM(H50:L50)-G50, 2)</f>
         <v/>
       </c>
@@ -4729,39 +4775,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="9" t="n">
+      <c r="D51" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="10" t="n">
         <v>1100.81</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F51" s="10" t="n">
         <v>36.96</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G51" s="7" t="n">
         <v>11.09</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="10">
         <f>G51*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="10">
         <f>G51*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="10">
         <f>G51*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K51" s="9">
+      <c r="K51" s="10">
         <f>G51*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L51" s="9">
+      <c r="L51" s="10">
         <f>G51*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M51" s="9">
+      <c r="M51" s="10">
         <f>ROUND(SUM(H51:L51)-G51, 2)</f>
         <v/>
       </c>
@@ -4782,39 +4828,39 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="9">
+      <c r="D52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="10">
         <f>G52*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="10">
         <f>G52*GP_Consultant_Pct</f>
         <v/>
       </c>
-      <c r="J52" s="9">
+      <c r="J52" s="10">
         <f>G52*GP_Raj_Pct</f>
         <v/>
       </c>
-      <c r="K52" s="9">
+      <c r="K52" s="10">
         <f>G52*GP_Nairne_Pct</f>
         <v/>
       </c>
-      <c r="L52" s="9">
+      <c r="L52" s="10">
         <f>G52*GP_Alec_Pct</f>
         <v/>
       </c>
-      <c r="M52" s="9">
+      <c r="M52" s="10">
         <f>ROUND(SUM(H52:L52)-G52, 2)</f>
         <v/>
       </c>
@@ -4861,7 +4907,7 @@
         <f>SUM(L2:L52)</f>
         <v/>
       </c>
-      <c r="M53" s="9">
+      <c r="M53" s="10">
         <f>ROUND(SUM(H53:L53)-G53, 2)</f>
         <v/>
       </c>
@@ -4877,50 +4923,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Consultant</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t># Investors</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Capital Raised</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Gross GP</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>% of GP Pool</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Weighted Expense</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Net Profit</t>
         </is>
@@ -4936,11 +4982,11 @@
         <f>COUNTIF(PI_Consultant, A2)</f>
         <v/>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <f>SUMIF(PI_Consultant, A2, PI_Capital)</f>
         <v/>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <f>SUMIF(PI_Consultant, A2, PI_ConsultantCut)</f>
         <v/>
       </c>
@@ -4948,11 +4994,11 @@
         <f>IFERROR(D2/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F2" s="9">
-        <f>IFERROR(D2/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G2" s="9">
+      <c r="F2" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A2, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G2" s="10">
         <f>D2-F2</f>
         <v/>
       </c>
@@ -4967,11 +5013,11 @@
         <f>COUNTIF(PI_Consultant, A3)</f>
         <v/>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <f>SUMIF(PI_Consultant, A3, PI_Capital)</f>
         <v/>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="10">
         <f>SUMIF(PI_Consultant, A3, PI_ConsultantCut)</f>
         <v/>
       </c>
@@ -4979,11 +5025,11 @@
         <f>IFERROR(D3/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F3" s="9">
-        <f>IFERROR(D3/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G3" s="9">
+      <c r="F3" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A3, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G3" s="10">
         <f>D3-F3</f>
         <v/>
       </c>
@@ -4998,11 +5044,11 @@
         <f>COUNTIF(PI_Consultant, A4)</f>
         <v/>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <f>SUMIF(PI_Consultant, A4, PI_Capital)</f>
         <v/>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <f>SUMIF(PI_Consultant, A4, PI_ConsultantCut)</f>
         <v/>
       </c>
@@ -5010,11 +5056,11 @@
         <f>IFERROR(D4/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F4" s="9">
-        <f>IFERROR(D4/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G4" s="9">
+      <c r="F4" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A4, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="10">
         <f>D4-F4</f>
         <v/>
       </c>
@@ -5029,11 +5075,11 @@
         <f>COUNTIF(PI_Consultant, A5)</f>
         <v/>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <f>SUMIF(PI_Consultant, A5, PI_Capital)</f>
         <v/>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <f>SUMIF(PI_Consultant, A5, PI_ConsultantCut)</f>
         <v/>
       </c>
@@ -5041,11 +5087,11 @@
         <f>IFERROR(D5/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F5" s="9">
-        <f>IFERROR(D5/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G5" s="9">
+      <c r="F5" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A5, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="10">
         <f>D5-F5</f>
         <v/>
       </c>
@@ -5060,11 +5106,11 @@
         <f>COUNTIF(PI_Consultant, A6)</f>
         <v/>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <f>SUMIF(PI_Consultant, A6, PI_Capital)</f>
         <v/>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="10">
         <f>SUMIF(PI_Consultant, A6, PI_ConsultantCut)</f>
         <v/>
       </c>
@@ -5072,11 +5118,11 @@
         <f>IFERROR(D6/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F6" s="9">
-        <f>IFERROR(D6/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G6" s="9">
+      <c r="F6" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A6, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="10">
         <f>D6-F6</f>
         <v/>
       </c>
@@ -5136,7 +5182,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="10">
         <f>SUM(PI_PerfFee)*GP_FundMgmt_Pct</f>
         <v/>
       </c>
@@ -5144,11 +5190,11 @@
         <f>IFERROR(D10/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F10" s="9">
-        <f>IFERROR(D10/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G10" s="9">
+      <c r="F10" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A10, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="10">
         <f>D10-F10</f>
         <v/>
       </c>
@@ -5169,7 +5215,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="10">
         <f>SUM(PI_PerfFee)*GP_Raj_Pct</f>
         <v/>
       </c>
@@ -5177,11 +5223,11 @@
         <f>IFERROR(D11/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F11" s="9">
-        <f>IFERROR(D11/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G11" s="9">
+      <c r="F11" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A11, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="10">
         <f>D11-F11</f>
         <v/>
       </c>
@@ -5202,7 +5248,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="10">
         <f>SUM(PI_PerfFee)*GP_Nairne_Pct</f>
         <v/>
       </c>
@@ -5210,11 +5256,11 @@
         <f>IFERROR(D12/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F12" s="9">
-        <f>IFERROR(D12/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G12" s="9">
+      <c r="F12" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A12, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="10">
         <f>D12-F12</f>
         <v/>
       </c>
@@ -5235,7 +5281,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="10">
         <f>SUM(PI_PerfFee)*GP_Alec_Pct</f>
         <v/>
       </c>
@@ -5243,11 +5289,11 @@
         <f>IFERROR(D13/$D$14,0)</f>
         <v/>
       </c>
-      <c r="F13" s="9">
-        <f>IFERROR(D13/$D$14,0)*Expense_Pool</f>
-        <v/>
-      </c>
-      <c r="G13" s="9">
+      <c r="F13" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A13, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="10">
         <f>D13-F13</f>
         <v/>
       </c>
@@ -5269,11 +5315,76 @@
         <v/>
       </c>
       <c r="F14" s="12">
-        <f>Expense_Pool</f>
+        <f>SUM(F2:F6)+SUM(F10:F13)</f>
         <v/>
       </c>
       <c r="G14" s="12">
         <f>D14-F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>EXTERNAL — TruQuant (18% upstream of Armada's books)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>TruQuant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="10">
+        <f>TQ_Income</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A17, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="10">
+        <f>D17-F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (Armada + TQ)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="12">
+        <f>D14+D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="12">
+        <f>F14+F17</f>
+        <v/>
+      </c>
+      <c r="G19" s="12">
+        <f>D19-F19</f>
         <v/>
       </c>
     </row>
@@ -5288,19 +5399,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Operating Costs</t>
+          <t>Costs — Allocation by Payor Group</t>
         </is>
       </c>
     </row>
@@ -5311,332 +5432,699 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>% of Pool</t>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>Payor Groups: 'TQ/Armada' = split among everyone (incl. TruQuant) by income share. 'Armada' = split among Armada parties only (excludes TruQuant) by income. 'Fund Management' = 100% Fund Mgmt.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Chris</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D5" s="13">
-        <f>B5/Costs_Total</f>
-        <v/>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Expense Item</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Payor Group</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Fund Hub SPV (Pending Split)</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Fund Mgmt</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>TruQuant</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Raj (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>Nairne (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TPA</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="13">
-        <f>B6/Costs_Total</f>
-        <v/>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>TQ/Armada</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>125.29</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1196.17</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>133.02</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>314.35</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>2748.24</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>3381.1</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>23.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chris (Hotel+Ticket)</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>3226.17</v>
-      </c>
-      <c r="D7" s="13">
-        <f>B7/Costs_Total</f>
-        <v/>
+          <t>TPA</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Armada</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>310.77</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>81.67</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>714</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Charalece</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D8" s="13">
-        <f>B8/Costs_Total</f>
-        <v/>
+          <t>Chris (Hotel+Ticket)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>3226.17</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>TQ/Armada</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>482.38</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>126.77</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>1108.29</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>9.31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alec (Ticket)</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>886</v>
-      </c>
-      <c r="D9" s="13">
-        <f>B9/Costs_Total</f>
-        <v/>
+          <t>Charalece</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Armada</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1035.89</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>272.23</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>28.18</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>2380</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alec (Hotel)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>1172</v>
-      </c>
-      <c r="D10" s="13">
-        <f>B10/Costs_Total</f>
-        <v/>
+          <t>Alec (Ticket)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>886</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Fund Management</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>886</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Taxes</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>6750</v>
-      </c>
-      <c r="D11" s="13">
-        <f>B11/Costs_Total</f>
-        <v/>
+          <t>Alec (Hotel)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>1172</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Fund Management</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>1172</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>6750</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Armada</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>1748.06</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>459.39</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>4016.25</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>33.75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
+      <c r="B13" s="7" t="n">
         <v>26000</v>
       </c>
-      <c r="D12" s="13">
-        <f>B12/Costs_Total</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Armada</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>705.28</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>6733.29</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>748.78</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>1769.49</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>183.16</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>15470</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="12">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="13">
-        <f>SUM(D5:D12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Allocation by GP %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="B14" s="12">
+        <f>SUM(B6:B13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="12">
+        <f>SUM(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>SUM(F6:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>SUM(G6:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="12">
+        <f>SUM(H6:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="12">
+        <f>SUM(I6:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="12">
+        <f>SUM(J6:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="12">
+        <f>SUM(K6:K13)</f>
+        <v/>
+      </c>
+      <c r="L14" s="12">
+        <f>SUM(L6:L13)</f>
+        <v/>
+      </c>
+      <c r="M14" s="12">
+        <f>SUM(M6:M13)</f>
+        <v/>
+      </c>
+      <c r="N14" s="12">
+        <f>SUM(N6:N13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Income Reference (used for cost weighting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Party</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>% of GP Pool</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Allocated Expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AJ Affleck</t>
-        </is>
-      </c>
-      <c r="B17" s="13">
-        <f>IFERROR(VLOOKUP(A17,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C17" s="9">
-        <f>B17*Costs_Total</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Alec Atkinson</t>
-        </is>
-      </c>
-      <c r="B18" s="13">
-        <f>IFERROR(VLOOKUP(A18,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="9">
-        <f>B18*Costs_Total</f>
-        <v/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>% TQ+Armada</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>% Armada-only</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fund Hub SPV (Pending Split)</t>
-        </is>
-      </c>
-      <c r="B19" s="13">
-        <f>IFERROR(VLOOKUP(A19,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C19" s="9">
-        <f>B19*Costs_Total</f>
-        <v/>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>3293.22</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>0.01566156528291167</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>0.02712606283373016</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
-        <f>IFERROR(VLOOKUP(A20,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C20" s="9">
-        <f>B20*Costs_Total</f>
-        <v/>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>31440.36</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>0.1495209636632215</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>0.2589725217130014</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="B21" s="13">
-        <f>IFERROR(VLOOKUP(A21,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C21" s="9">
-        <f>B21*Costs_Total</f>
-        <v/>
+          <t>Fund Hub SPV (Pending Split)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>3496.35</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0.01662761667864213</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>0.02879927814700346</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fund Mgmt</t>
-        </is>
-      </c>
-      <c r="B22" s="13">
-        <f>IFERROR(VLOOKUP(A22,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C22" s="9">
-        <f>B22*Costs_Total</f>
-        <v/>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>8262.459999999999</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>0.03929378719646822</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0.06805742090349085</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raj (GP fixed 0.5%)</t>
-        </is>
-      </c>
-      <c r="B23" s="13">
-        <f>IFERROR(VLOOKUP(A23,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C23" s="9">
-        <f>B23*Costs_Total</f>
-        <v/>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>855.26</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0.004067353471748701</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.007044716402774138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nairne (GP fixed 0.5%)</t>
-        </is>
-      </c>
-      <c r="B24" s="13">
-        <f>IFERROR(VLOOKUP(A24,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C24" s="9">
-        <f>B24*Costs_Total</f>
-        <v/>
+          <t>Fund Mgmt</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>72235.50999999999</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0.3435305521649496</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>0.595</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>TruQuant</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n">
+        <v>88869.69</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>0.4226377274538662</v>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Raj (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>607.02</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>0.002886811362730669</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nairne (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
+        <v>607.02</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>0.002886811362730669</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Alec (GP fixed 0.5%)</t>
         </is>
       </c>
-      <c r="B25" s="13">
-        <f>IFERROR(VLOOKUP(A25,'Consultant Summary'!$A$2:$E$14,5,FALSE),0)</f>
-        <v/>
-      </c>
-      <c r="C25" s="9">
-        <f>B25*Costs_Total</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B26" s="16">
-        <f>SUM(B17:B25)</f>
-        <v/>
-      </c>
-      <c r="C26" s="12">
-        <f>SUM(C17:C25)</f>
-        <v/>
+      <c r="B28" s="10" t="n">
+        <v>607.02</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>0.002886811362730669</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>0.005</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5686,7 +6174,7 @@
           <t>Sum of per-investor Perf Fee (GP pool from TPA)</t>
         </is>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="10">
         <f>SUM(PI_PerfFee)</f>
         <v/>
       </c>
@@ -5702,7 +6190,7 @@
           <t>Sum of all per-investor split columns (H–L)</t>
         </is>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="10">
         <f>'Per-Investor Allocation'!H53+'Per-Investor Allocation'!I53+'Per-Investor Allocation'!J53+'Per-Investor Allocation'!K53+'Per-Investor Allocation'!L53</f>
         <v/>
       </c>

--- a/Armada_Consultant_Splits.xlsx
+++ b/Armada_Consultant_Splits.xlsx
@@ -118,7 +118,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002a3550"/>
+        <fgColor rgb="00d9ead3"/>
       </patternFill>
     </fill>
     <fill>

--- a/Armada_Consultant_Splits.xlsx
+++ b/Armada_Consultant_Splits.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Investor Allocation" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consultant Summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="GP_FundMgmt_Pct">Inputs!$B$5</definedName>
@@ -32,6 +33,9 @@
     <definedName name="Costs_PartyHeaders">Costs!$E$5:$N$5</definedName>
     <definedName name="Costs_PartyTotals">Costs!$E$14:$N$14</definedName>
     <definedName name="Costs_Total">Costs!$B$14</definedName>
+    <definedName name="Dist_Type">Distributions!$C$10:$C$22</definedName>
+    <definedName name="Dist_Party">Distributions!$D$10:$D$22</definedName>
+    <definedName name="Dist_Amount">Distributions!$F$10:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +46,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +112,16 @@
       <i val="1"/>
       <color rgb="00a78bfa"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400e"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001e3a8a"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +141,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00334155"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fef3c7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00dbeafe"/>
       </patternFill>
     </fill>
   </fills>
@@ -158,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -191,6 +213,19 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6136,6 +6171,582 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GP Pool Distribution Tracker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Period: Mar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Pool Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Total GP Pool</t>
+        </is>
+      </c>
+      <c r="B5" s="10">
+        <f>SUM(PI_PerfFee)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Cash Distributed (this period)</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <f>F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Remaining in Pool</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>B5-B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Distributions Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Party / Payee</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr"/>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Royal KKS Collective + Atkinson Group + Chris March (per app screenshot)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>56026</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Includes Feb/March reimbursements — Nairne, Chris hotel/ticket, Charalece, Alec NYC, Taxes, Chris</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="25" t="inlineStr"/>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Payout</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fund Mgmt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Management cut (partial)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>30604.06</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr"/>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Payout</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Consultant cut (partial)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>937.76</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F23" s="12">
+        <f>SUM(F10:F22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Per-Party Settlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Party</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Expected Net</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Cash Paid Out</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Outstanding</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Suggested Recipient / Wire Info</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AJ Affleck</t>
+        </is>
+      </c>
+      <c r="B27" s="10">
+        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C27" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A27, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D27" s="10">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="28" t="inlineStr"/>
+      <c r="F27">
+        <f>IF(ROUND(D27,2)=0,"Settled",IF(ROUND(D27,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="B28" s="10">
+        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C28" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A28, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D28" s="10">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="28" t="inlineStr"/>
+      <c r="F28">
+        <f>IF(ROUND(D28,2)=0,"Settled",IF(ROUND(D28,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Fund Hub SPV (Pending Split)</t>
+        </is>
+      </c>
+      <c r="B29" s="10">
+        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C29" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A29, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D29" s="10">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="28" t="inlineStr"/>
+      <c r="F29">
+        <f>IF(ROUND(D29,2)=0,"Settled",IF(ROUND(D29,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jake Gordon</t>
+        </is>
+      </c>
+      <c r="B30" s="10">
+        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C30" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A30, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D30" s="10">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="28" t="inlineStr"/>
+      <c r="F30">
+        <f>IF(ROUND(D30,2)=0,"Settled",IF(ROUND(D30,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="B31" s="10">
+        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C31" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A31, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D31" s="10">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="28" t="inlineStr"/>
+      <c r="F31">
+        <f>IF(ROUND(D31,2)=0,"Settled",IF(ROUND(D31,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fund Mgmt</t>
+        </is>
+      </c>
+      <c r="B32" s="10">
+        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C32" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A32, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D32" s="10">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="28" t="inlineStr"/>
+      <c r="F32">
+        <f>IF(ROUND(D32,2)=0,"Settled",IF(ROUND(D32,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Raj (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B33" s="10">
+        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C33" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A33, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D33" s="10">
+        <f>B33-C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="28" t="inlineStr"/>
+      <c r="F33">
+        <f>IF(ROUND(D33,2)=0,"Settled",IF(ROUND(D33,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Nairne (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B34" s="10">
+        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C34" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A34, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D34" s="10">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="28" t="inlineStr"/>
+      <c r="F34">
+        <f>IF(ROUND(D34,2)=0,"Settled",IF(ROUND(D34,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B35" s="10">
+        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A35, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="D35" s="10">
+        <f>B35-C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="28" t="inlineStr"/>
+      <c r="F35">
+        <f>IF(ROUND(D35,2)=0,"Settled",IF(ROUND(D35,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL (Armada GP Pool)</t>
+        </is>
+      </c>
+      <c r="B36" s="12">
+        <f>SUM(B27:B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="12">
+        <f>SUM(C27:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="12">
+        <f>SUM(D27:D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>External (does not draw from this pool)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>TruQuant</t>
+        </is>
+      </c>
+      <c r="B38" s="10">
+        <f>TQ_Income-IFERROR(INDEX(Costs_PartyTotals, MATCH(A38, Costs_PartyHeaders, 0)),0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>External — TruQuant's 18% comes upstream of this pool. Their share of TQ/Armada costs is also paid externally.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>Note: Expenses (vendor cash) reduce the pool but don't count toward any party's Cash Paid Out — only Payout-type distributions do. Cash Paid Out aggregates from the Distributions Log via SUMIFS on Type='Payout'. To record a new transfer, add a row in the Distributions Log above and the Settlement table updates automatically.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A40:I40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Armada_Consultant_Splits.xlsx
+++ b/Armada_Consultant_Splits.xlsx
@@ -6174,15 +6174,15 @@
   <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6428,25 +6428,35 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
+          <t>Expected Gross</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Weighted Expense</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
           <t>Expected Net</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Cash Paid Out</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>Outstanding</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Suggested Recipient / Wire Info</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -6459,20 +6469,28 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A27, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D27" s="10">
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="E27" s="28" t="inlineStr"/>
-      <c r="F27">
-        <f>IF(ROUND(D27,2)=0,"Settled",IF(ROUND(D27,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E27" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A27, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F27" s="10">
+        <f>D27-E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="28" t="inlineStr"/>
+      <c r="H27">
+        <f>IF(ROUND(F27,2)=0,"Settled",IF(ROUND(F27,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6483,20 +6501,28 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A28, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D28" s="10">
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="E28" s="28" t="inlineStr"/>
-      <c r="F28">
-        <f>IF(ROUND(D28,2)=0,"Settled",IF(ROUND(D28,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E28" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A28, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f>D28-E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="28" t="inlineStr"/>
+      <c r="H28">
+        <f>IF(ROUND(F28,2)=0,"Settled",IF(ROUND(F28,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6507,20 +6533,28 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A29, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D29" s="10">
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="E29" s="28" t="inlineStr"/>
-      <c r="F29">
-        <f>IF(ROUND(D29,2)=0,"Settled",IF(ROUND(D29,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E29" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A29, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F29" s="10">
+        <f>D29-E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="28" t="inlineStr"/>
+      <c r="H29">
+        <f>IF(ROUND(F29,2)=0,"Settled",IF(ROUND(F29,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6531,20 +6565,28 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A30, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D30" s="10">
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="E30" s="28" t="inlineStr"/>
-      <c r="F30">
-        <f>IF(ROUND(D30,2)=0,"Settled",IF(ROUND(D30,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E30" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A30, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>D30-E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="28" t="inlineStr"/>
+      <c r="H30">
+        <f>IF(ROUND(F30,2)=0,"Settled",IF(ROUND(F30,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6555,20 +6597,28 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A31, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D31" s="10">
         <f>B31-C31</f>
         <v/>
       </c>
-      <c r="E31" s="28" t="inlineStr"/>
-      <c r="F31">
-        <f>IF(ROUND(D31,2)=0,"Settled",IF(ROUND(D31,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E31" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A31, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>D31-E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="28" t="inlineStr"/>
+      <c r="H31">
+        <f>IF(ROUND(F31,2)=0,"Settled",IF(ROUND(F31,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6579,20 +6629,28 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A32, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D32" s="10">
         <f>B32-C32</f>
         <v/>
       </c>
-      <c r="E32" s="28" t="inlineStr"/>
-      <c r="F32">
-        <f>IF(ROUND(D32,2)=0,"Settled",IF(ROUND(D32,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E32" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A32, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>D32-E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="28" t="inlineStr"/>
+      <c r="H32">
+        <f>IF(ROUND(F32,2)=0,"Settled",IF(ROUND(F32,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6603,20 +6661,28 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A33, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D33" s="10">
         <f>B33-C33</f>
         <v/>
       </c>
-      <c r="E33" s="28" t="inlineStr"/>
-      <c r="F33">
-        <f>IF(ROUND(D33,2)=0,"Settled",IF(ROUND(D33,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E33" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A33, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f>D33-E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="28" t="inlineStr"/>
+      <c r="H33">
+        <f>IF(ROUND(F33,2)=0,"Settled",IF(ROUND(F33,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6627,20 +6693,28 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A34, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D34" s="10">
         <f>B34-C34</f>
         <v/>
       </c>
-      <c r="E34" s="28" t="inlineStr"/>
-      <c r="F34">
-        <f>IF(ROUND(D34,2)=0,"Settled",IF(ROUND(D34,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E34" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A34, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>D34-E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="28" t="inlineStr"/>
+      <c r="H34">
+        <f>IF(ROUND(F34,2)=0,"Settled",IF(ROUND(F34,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6651,20 +6725,28 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$19, 7, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>SUMIFS(Dist_Amount, Dist_Party, A35, Dist_Type, "Payout")</f>
+        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D35" s="10">
         <f>B35-C35</f>
         <v/>
       </c>
-      <c r="E35" s="28" t="inlineStr"/>
-      <c r="F35">
-        <f>IF(ROUND(D35,2)=0,"Settled",IF(ROUND(D35,2)&lt;0,"Overpaid","Outstanding"))</f>
+      <c r="E35" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A35, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>D35-E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="28" t="inlineStr"/>
+      <c r="H35">
+        <f>IF(ROUND(F35,2)=0,"Settled",IF(ROUND(F35,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
@@ -6686,6 +6768,14 @@
         <f>SUM(D27:D35)</f>
         <v/>
       </c>
+      <c r="E36" s="12">
+        <f>SUM(E27:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="12">
+        <f>SUM(F27:F35)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6701,25 +6791,33 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>TQ_Income-IFERROR(INDEX(Costs_PartyTotals, MATCH(A38, Costs_PartyHeaders, 0)),0)</f>
-        <v/>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
+        <f>TQ_Income</f>
+        <v/>
+      </c>
+      <c r="C38" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A38, Costs_PartyHeaders, 0)),0)</f>
+        <v/>
+      </c>
+      <c r="D38" s="10">
+        <f>B38-C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>External — TruQuant's 18% comes upstream of this pool. Their share of TQ/Armada costs is also paid externally.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>External</t>
         </is>

--- a/Armada_Consultant_Splits.xlsx
+++ b/Armada_Consultant_Splits.xlsx
@@ -23,15 +23,16 @@
     <definedName name="GP_Alec_Pct">Inputs!$B$9</definedName>
     <definedName name="Expense_Pool">Inputs!$B$14</definedName>
     <definedName name="TQ_Income">Inputs!$B$17</definedName>
-    <definedName name="IDS_TPA">'IDS Mapping'!$A$2:$A$52</definedName>
-    <definedName name="IDS_Consultant">'IDS Mapping'!$D$2:$D$52</definedName>
-    <definedName name="PI_Consultant">'Per-Investor Allocation'!$C$2:$C$52</definedName>
-    <definedName name="PI_PerfFee">'Per-Investor Allocation'!$G$2:$G$52</definedName>
-    <definedName name="PI_ConsultantCut">'Per-Investor Allocation'!$I$2:$I$52</definedName>
-    <definedName name="PI_FundMgmt">'Per-Investor Allocation'!$H$2:$H$52</definedName>
-    <definedName name="PI_Capital">'Per-Investor Allocation'!$E$2:$E$52</definedName>
-    <definedName name="Costs_PartyHeaders">Costs!$E$5:$N$5</definedName>
-    <definedName name="Costs_PartyTotals">Costs!$E$14:$N$14</definedName>
+    <definedName name="IDS_TPA">'IDS Mapping'!$A$2:$A$53</definedName>
+    <definedName name="IDS_Consultant">'IDS Mapping'!$D$2:$D$53</definedName>
+    <definedName name="PI_Consultant">'Per-Investor Allocation'!$C$2:$C$53</definedName>
+    <definedName name="PI_PerfFee">'Per-Investor Allocation'!$G$2:$G$53</definedName>
+    <definedName name="PI_ConsultantCut">'Per-Investor Allocation'!$I$2:$I$53</definedName>
+    <definedName name="PI_FundMgmt">'Per-Investor Allocation'!$H$2:$H$53</definedName>
+    <definedName name="PI_Capital">'Per-Investor Allocation'!$E$2:$E$53</definedName>
+    <definedName name="PI_Share">'Per-Investor Allocation'!$N$2:$N$53</definedName>
+    <definedName name="Costs_PartyHeaders">Costs!$E$5:$O$5</definedName>
+    <definedName name="Costs_PartyTotals">Costs!$E$14:$O$14</definedName>
     <definedName name="Costs_Total">Costs!$B$14</definedName>
     <definedName name="Dist_Type">Distributions!$C$10:$C$22</definedName>
     <definedName name="Dist_Party">Distributions!$D$10:$D$22</definedName>
@@ -46,7 +47,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +76,10 @@
       <b val="1"/>
       <color rgb="00e2e8f0"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00b45309"/>
     </font>
     <font>
       <b val="1"/>
@@ -180,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,31 +201,35 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -747,7 +756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1670,7 +1679,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Craig Levinson</t>
+          <t>Craig Levinson  [AJ Affleck 50.0% share]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1692,22 +1701,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14-Class B-1060-1</t>
+          <t>14-Class B-1061-1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Daniel Welch Kirkham</t>
+          <t>Craig Levinson  [Raj (Split) 50.0% share]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INVCSD3092282</t>
+          <t>INVCSD1626047</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Raj (Split)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1719,22 +1728,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14-Class B-1059-1</t>
+          <t>14-Class B-1060-1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>John Charles Kirkham</t>
+          <t>Daniel Welch Kirkham</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INVCSD3092199</t>
+          <t>INVCSD3092282</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1746,22 +1755,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14-Class B-1064-1</t>
+          <t>14-Class B-1059-1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Advanta Trust Company Inc. FBO Shreekanth Karwande IRA 1522282</t>
+          <t>John Charles Kirkham</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INVCSD3092154</t>
+          <t>INVCSD3092199</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1773,22 +1782,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14-Class B-1037-1</t>
+          <t>14-Class B-1064-1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>James Lockhart</t>
+          <t>Advanta Trust Company Inc. FBO Shreekanth Karwande IRA 1522282</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>INVCSD1625337</t>
+          <t>INVCSD3092154</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1800,17 +1809,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14-Class B-1063-1</t>
+          <t>14-Class B-1037-1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lyman Phillips</t>
+          <t>James Lockhart</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INVCSD3093225</t>
+          <t>INVCSD1625337</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1827,17 +1836,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14-Class B-1062-1</t>
+          <t>14-Class B-1063-1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lori Brennan</t>
+          <t>Lyman Phillips</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INVCSD3092104</t>
+          <t>INVCSD3093225</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1854,17 +1863,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14-Class B-1066-1</t>
+          <t>14-Class B-1062-1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brandy and Adam Fisher</t>
+          <t>Lori Brennan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INVCSD3136488</t>
+          <t>INVCSD3092104</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1881,12 +1890,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14-Class B-1072-1</t>
+          <t>14-Class B-1066-1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mashirito LLC</t>
+          <t>Brandy and Adam Fisher</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INVCSD3136488</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1896,19 +1910,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Override (confirmed 2026-04-27)</t>
+          <t>TPA + IDS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14-Class B-1068-1</t>
+          <t>14-Class B-1072-1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Weston Shea Christensen</t>
+          <t>Mashirito LLC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1925,17 +1939,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14-Class B-1002-1</t>
+          <t>14-Class B-1068-1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frieda Goldsmith 1998 Trust</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Armada3</t>
+          <t>Weston Shea Christensen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1945,29 +1954,29 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TPA + IDS</t>
+          <t>Override (confirmed 2026-04-27)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14-Class B-1056-1</t>
+          <t>14-Class B-1002-1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Richard Gordon</t>
+          <t>Frieda Goldsmith 1998 Trust</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INVCSD1624351</t>
+          <t>Armada3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1979,20 +1988,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14-Class B-1004-1</t>
+          <t>14-Class B-1056-1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Golden Touch Properties LLC</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2123050</v>
+          <t>Richard Gordon</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INVCSD1624351</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2004,20 +2015,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14-Class B-1015-1</t>
+          <t>14-Class B-1004-1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Treyson Gordon</t>
+          <t>Golden Touch Properties LLC</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2223754</v>
+        <v>2123050</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2029,20 +2040,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>14-Class B-1025-1</t>
+          <t>14-Class B-1015-1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Atkinson Group LLC</t>
+          <t>Treyson Gordon</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2056299</v>
+        <v>2223754</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2054,16 +2065,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14-Class B-1010-1</t>
+          <t>14-Class B-1025-1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchell Squires</t>
+          <t>The Atkinson Group LLC</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2060557</v>
+        <v>2056299</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2079,23 +2090,48 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>14-Class B-1010-1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mitchell Squires</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2060557</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>TPA + IDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>14-Class B-1024-1</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Joel Guy and Jennifer Pasetes</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C53" t="n">
         <v>2053225</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>TPA + IDS</t>
         </is>
@@ -2112,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2128,6 +2164,7 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="29" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2196,6 +2233,11 @@
           <t>Sum Check</t>
         </is>
       </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2249,6 +2291,9 @@
         <f>ROUND(SUM(H2:L2)-G2, 2)</f>
         <v/>
       </c>
+      <c r="N2" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2302,6 +2347,9 @@
         <f>ROUND(SUM(H3:L3)-G3, 2)</f>
         <v/>
       </c>
+      <c r="N3" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2355,6 +2403,9 @@
         <f>ROUND(SUM(H4:L4)-G4, 2)</f>
         <v/>
       </c>
+      <c r="N4" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2408,6 +2459,9 @@
         <f>ROUND(SUM(H5:L5)-G5, 2)</f>
         <v/>
       </c>
+      <c r="N5" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2461,6 +2515,9 @@
         <f>ROUND(SUM(H6:L6)-G6, 2)</f>
         <v/>
       </c>
+      <c r="N6" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2514,6 +2571,9 @@
         <f>ROUND(SUM(H7:L7)-G7, 2)</f>
         <v/>
       </c>
+      <c r="N7" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2567,6 +2627,9 @@
         <f>ROUND(SUM(H8:L8)-G8, 2)</f>
         <v/>
       </c>
+      <c r="N8" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2620,6 +2683,9 @@
         <f>ROUND(SUM(H9:L9)-G9, 2)</f>
         <v/>
       </c>
+      <c r="N9" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2673,6 +2739,9 @@
         <f>ROUND(SUM(H10:L10)-G10, 2)</f>
         <v/>
       </c>
+      <c r="N10" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2726,6 +2795,9 @@
         <f>ROUND(SUM(H11:L11)-G11, 2)</f>
         <v/>
       </c>
+      <c r="N11" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2779,6 +2851,9 @@
         <f>ROUND(SUM(H12:L12)-G12, 2)</f>
         <v/>
       </c>
+      <c r="N12" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2832,6 +2907,9 @@
         <f>ROUND(SUM(H13:L13)-G13, 2)</f>
         <v/>
       </c>
+      <c r="N13" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2885,6 +2963,9 @@
         <f>ROUND(SUM(H14:L14)-G14, 2)</f>
         <v/>
       </c>
+      <c r="N14" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2938,6 +3019,9 @@
         <f>ROUND(SUM(H15:L15)-G15, 2)</f>
         <v/>
       </c>
+      <c r="N15" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2991,6 +3075,9 @@
         <f>ROUND(SUM(H16:L16)-G16, 2)</f>
         <v/>
       </c>
+      <c r="N16" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3044,6 +3131,9 @@
         <f>ROUND(SUM(H17:L17)-G17, 2)</f>
         <v/>
       </c>
+      <c r="N17" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3097,6 +3187,9 @@
         <f>ROUND(SUM(H18:L18)-G18, 2)</f>
         <v/>
       </c>
+      <c r="N18" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3150,6 +3243,9 @@
         <f>ROUND(SUM(H19:L19)-G19, 2)</f>
         <v/>
       </c>
+      <c r="N19" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3203,6 +3299,9 @@
         <f>ROUND(SUM(H20:L20)-G20, 2)</f>
         <v/>
       </c>
+      <c r="N20" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3256,6 +3355,9 @@
         <f>ROUND(SUM(H21:L21)-G21, 2)</f>
         <v/>
       </c>
+      <c r="N21" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3309,6 +3411,9 @@
         <f>ROUND(SUM(H22:L22)-G22, 2)</f>
         <v/>
       </c>
+      <c r="N22" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3362,6 +3467,9 @@
         <f>ROUND(SUM(H23:L23)-G23, 2)</f>
         <v/>
       </c>
+      <c r="N23" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3415,6 +3523,9 @@
         <f>ROUND(SUM(H24:L24)-G24, 2)</f>
         <v/>
       </c>
+      <c r="N24" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3468,6 +3579,9 @@
         <f>ROUND(SUM(H25:L25)-G25, 2)</f>
         <v/>
       </c>
+      <c r="N25" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3521,6 +3635,9 @@
         <f>ROUND(SUM(H26:L26)-G26, 2)</f>
         <v/>
       </c>
+      <c r="N26" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3574,6 +3691,9 @@
         <f>ROUND(SUM(H27:L27)-G27, 2)</f>
         <v/>
       </c>
+      <c r="N27" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3627,6 +3747,9 @@
         <f>ROUND(SUM(H28:L28)-G28, 2)</f>
         <v/>
       </c>
+      <c r="N28" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3680,6 +3803,9 @@
         <f>ROUND(SUM(H29:L29)-G29, 2)</f>
         <v/>
       </c>
+      <c r="N29" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3733,6 +3859,9 @@
         <f>ROUND(SUM(H30:L30)-G30, 2)</f>
         <v/>
       </c>
+      <c r="N30" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3786,6 +3915,9 @@
         <f>ROUND(SUM(H31:L31)-G31, 2)</f>
         <v/>
       </c>
+      <c r="N31" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3839,6 +3971,9 @@
         <f>ROUND(SUM(H32:L32)-G32, 2)</f>
         <v/>
       </c>
+      <c r="N32" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3892,6 +4027,9 @@
         <f>ROUND(SUM(H33:L33)-G33, 2)</f>
         <v/>
       </c>
+      <c r="N33" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3945,6 +4083,9 @@
         <f>ROUND(SUM(H34:L34)-G34, 2)</f>
         <v/>
       </c>
+      <c r="N34" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3998,6 +4139,9 @@
         <f>ROUND(SUM(H35:L35)-G35, 2)</f>
         <v/>
       </c>
+      <c r="N35" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4005,9 +4149,9 @@
           <t>14-Class B-1061-1</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Craig Levinson</t>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Craig Levinson  [AJ Affleck 50.0% share]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4019,13 +4163,13 @@
         <v>0</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>109173.32</v>
+        <v>54586.66</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>3666</v>
+        <v>1833</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1099.8</v>
+        <v>549.9</v>
       </c>
       <c r="H36" s="10">
         <f>G36*GP_FundMgmt_Pct</f>
@@ -4051,34 +4195,37 @@
         <f>ROUND(SUM(H36:L36)-G36, 2)</f>
         <v/>
       </c>
+      <c r="N36" s="13" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14-Class B-1060-1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Daniel Welch Kirkham</t>
+          <t>14-Class B-1061-1</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Craig Levinson  [Raj (Split) 50.0% share]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Raj (Split)</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>109123.67</v>
+        <v>54586.66</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>3664.33</v>
+        <v>1833</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>1099.3</v>
+        <v>549.9</v>
       </c>
       <c r="H37" s="10">
         <f>G37*GP_FundMgmt_Pct</f>
@@ -4104,21 +4251,24 @@
         <f>ROUND(SUM(H37:L37)-G37, 2)</f>
         <v/>
       </c>
+      <c r="N37" s="13" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14-Class B-1059-1</t>
+          <t>14-Class B-1060-1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>John Charles Kirkham</t>
+          <t>Daniel Welch Kirkham</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
@@ -4157,34 +4307,37 @@
         <f>ROUND(SUM(H38:L38)-G38, 2)</f>
         <v/>
       </c>
+      <c r="N38" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14-Class B-1064-1</t>
+          <t>14-Class B-1059-1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Advanta Trust Company Inc. FBO Shreekanth Karwande IRA 1522282</t>
+          <t>John Charles Kirkham</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>108565.29</v>
+        <v>109123.67</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>3645.58</v>
+        <v>3664.33</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>1093.67</v>
+        <v>1099.3</v>
       </c>
       <c r="H39" s="10">
         <f>G39*GP_FundMgmt_Pct</f>
@@ -4210,34 +4363,37 @@
         <f>ROUND(SUM(H39:L39)-G39, 2)</f>
         <v/>
       </c>
+      <c r="N39" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14-Class B-1037-1</t>
+          <t>14-Class B-1064-1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>James Lockhart</t>
+          <t>Advanta Trust Company Inc. FBO Shreekanth Karwande IRA 1522282</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>104520.17</v>
+        <v>108565.29</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>3509.75</v>
+        <v>3645.58</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>1052.92</v>
+        <v>1093.67</v>
       </c>
       <c r="H40" s="10">
         <f>G40*GP_FundMgmt_Pct</f>
@@ -4263,16 +4419,19 @@
         <f>ROUND(SUM(H40:L40)-G40, 2)</f>
         <v/>
       </c>
+      <c r="N40" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14-Class B-1063-1</t>
+          <t>14-Class B-1037-1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lyman Phillips</t>
+          <t>James Lockhart</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4284,13 +4443,13 @@
         <v>0</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>103481.71</v>
+        <v>104520.17</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>3474.88</v>
+        <v>3509.75</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>1042.46</v>
+        <v>1052.92</v>
       </c>
       <c r="H41" s="10">
         <f>G41*GP_FundMgmt_Pct</f>
@@ -4316,16 +4475,19 @@
         <f>ROUND(SUM(H41:L41)-G41, 2)</f>
         <v/>
       </c>
+      <c r="N41" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14-Class B-1062-1</t>
+          <t>14-Class B-1063-1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lori Brennan</t>
+          <t>Lyman Phillips</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4337,13 +4499,13 @@
         <v>0</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>103430.88</v>
+        <v>103481.71</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>3473.17</v>
+        <v>3474.88</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>1041.95</v>
+        <v>1042.46</v>
       </c>
       <c r="H42" s="10">
         <f>G42*GP_FundMgmt_Pct</f>
@@ -4369,16 +4531,19 @@
         <f>ROUND(SUM(H42:L42)-G42, 2)</f>
         <v/>
       </c>
+      <c r="N42" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14-Class B-1066-1</t>
+          <t>14-Class B-1062-1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brandy and Adam Fisher</t>
+          <t>Lori Brennan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4390,13 +4555,13 @@
         <v>0</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>103412.44</v>
+        <v>103430.88</v>
       </c>
       <c r="F43" s="10" t="n">
-        <v>3472.55</v>
+        <v>3473.17</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>1041.76</v>
+        <v>1041.95</v>
       </c>
       <c r="H43" s="10">
         <f>G43*GP_FundMgmt_Pct</f>
@@ -4422,16 +4587,19 @@
         <f>ROUND(SUM(H43:L43)-G43, 2)</f>
         <v/>
       </c>
+      <c r="N43" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14-Class B-1072-1</t>
+          <t>14-Class B-1066-1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mashirito LLC</t>
+          <t>Brandy and Adam Fisher</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4443,13 +4611,13 @@
         <v>0</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>102407.15</v>
+        <v>103412.44</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>3438.79</v>
+        <v>3472.55</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>1031.64</v>
+        <v>1041.76</v>
       </c>
       <c r="H44" s="10">
         <f>G44*GP_FundMgmt_Pct</f>
@@ -4475,16 +4643,19 @@
         <f>ROUND(SUM(H44:L44)-G44, 2)</f>
         <v/>
       </c>
+      <c r="N44" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14-Class B-1068-1</t>
+          <t>14-Class B-1072-1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Weston Shea Christensen</t>
+          <t>Mashirito LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4528,16 +4699,19 @@
         <f>ROUND(SUM(H45:L45)-G45, 2)</f>
         <v/>
       </c>
+      <c r="N45" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14-Class B-1002-1</t>
+          <t>14-Class B-1068-1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frieda Goldsmith 1998 Trust</t>
+          <t>Weston Shea Christensen</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4549,13 +4723,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>80692.28999999999</v>
+        <v>102407.15</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>2709.62</v>
+        <v>3438.79</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>812.88</v>
+        <v>1031.64</v>
       </c>
       <c r="H46" s="10">
         <f>G46*GP_FundMgmt_Pct</f>
@@ -4581,34 +4755,37 @@
         <f>ROUND(SUM(H46:L46)-G46, 2)</f>
         <v/>
       </c>
+      <c r="N46" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14-Class B-1056-1</t>
+          <t>14-Class B-1002-1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Richard Gordon</t>
+          <t>Frieda Goldsmith 1998 Trust</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>Alec Atkinson</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>78321.57000000001</v>
+        <v>80692.28999999999</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>2630.01</v>
+        <v>2709.62</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>789</v>
+        <v>812.88</v>
       </c>
       <c r="H47" s="10">
         <f>G47*GP_FundMgmt_Pct</f>
@@ -4634,34 +4811,37 @@
         <f>ROUND(SUM(H47:L47)-G47, 2)</f>
         <v/>
       </c>
+      <c r="N47" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14-Class B-1004-1</t>
+          <t>14-Class B-1056-1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Golden Touch Properties LLC</t>
+          <t>Richard Gordon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AJ Affleck</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>64305.85</v>
+        <v>78321.57000000001</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>2159.37</v>
+        <v>2630.01</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>647.8099999999999</v>
+        <v>789</v>
       </c>
       <c r="H48" s="10">
         <f>G48*GP_FundMgmt_Pct</f>
@@ -4687,34 +4867,37 @@
         <f>ROUND(SUM(H48:L48)-G48, 2)</f>
         <v/>
       </c>
+      <c r="N48" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14-Class B-1015-1</t>
+          <t>14-Class B-1004-1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Treyson Gordon</t>
+          <t>Golden Touch Properties LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jake Gordon</t>
+          <t>AJ Affleck</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>57066.22</v>
+        <v>64305.85</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>1916.26</v>
+        <v>2159.37</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>574.88</v>
+        <v>647.8099999999999</v>
       </c>
       <c r="H49" s="10">
         <f>G49*GP_FundMgmt_Pct</f>
@@ -4740,34 +4923,37 @@
         <f>ROUND(SUM(H49:L49)-G49, 2)</f>
         <v/>
       </c>
+      <c r="N49" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>14-Class B-1025-1</t>
+          <t>14-Class B-1015-1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Atkinson Group LLC</t>
+          <t>Treyson Gordon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alec Atkinson</t>
+          <t>Jake Gordon</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>41136.24</v>
+        <v>57066.22</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1381.34</v>
+        <v>1916.26</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>414.4</v>
+        <v>574.88</v>
       </c>
       <c r="H50" s="10">
         <f>G50*GP_FundMgmt_Pct</f>
@@ -4793,16 +4979,19 @@
         <f>ROUND(SUM(H50:L50)-G50, 2)</f>
         <v/>
       </c>
+      <c r="N50" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14-Class B-1010-1</t>
+          <t>14-Class B-1025-1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchell Squires</t>
+          <t>The Atkinson Group LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4814,13 +5003,13 @@
         <v>0</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>1100.81</v>
+        <v>41136.24</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>36.96</v>
+        <v>1381.34</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>11.09</v>
+        <v>414.4</v>
       </c>
       <c r="H51" s="10">
         <f>G51*GP_FundMgmt_Pct</f>
@@ -4846,16 +5035,19 @@
         <f>ROUND(SUM(H51:L51)-G51, 2)</f>
         <v/>
       </c>
+      <c r="N51" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14-Class B-1024-1</t>
+          <t>14-Class B-1010-1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Joel Guy and Jennifer Pasetes</t>
+          <t>Mitchell Squires</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4867,13 +5059,13 @@
         <v>0</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>1100.81</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>0</v>
+        <v>36.96</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0</v>
+        <v>11.09</v>
       </c>
       <c r="H52" s="10">
         <f>G52*GP_FundMgmt_Pct</f>
@@ -4899,51 +5091,114 @@
         <f>ROUND(SUM(H52:L52)-G52, 2)</f>
         <v/>
       </c>
+      <c r="N52" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
-      <c r="B53" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D53" s="12">
-        <f>SUM(D2:D52)</f>
-        <v/>
-      </c>
-      <c r="E53" s="12">
-        <f>SUM(E2:E52)</f>
-        <v/>
-      </c>
-      <c r="F53" s="12">
-        <f>SUM(F2:F52)</f>
-        <v/>
-      </c>
-      <c r="G53" s="12">
-        <f>SUM(G2:G52)</f>
-        <v/>
-      </c>
-      <c r="H53" s="12">
-        <f>SUM(H2:H52)</f>
-        <v/>
-      </c>
-      <c r="I53" s="12">
-        <f>SUM(I2:I52)</f>
-        <v/>
-      </c>
-      <c r="J53" s="12">
-        <f>SUM(J2:J52)</f>
-        <v/>
-      </c>
-      <c r="K53" s="12">
-        <f>SUM(K2:K52)</f>
-        <v/>
-      </c>
-      <c r="L53" s="12">
-        <f>SUM(L2:L52)</f>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14-Class B-1024-1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Joel Guy and Jennifer Pasetes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Alec Atkinson</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="10">
+        <f>G53*GP_FundMgmt_Pct</f>
+        <v/>
+      </c>
+      <c r="I53" s="10">
+        <f>G53*GP_Consultant_Pct</f>
+        <v/>
+      </c>
+      <c r="J53" s="10">
+        <f>G53*GP_Raj_Pct</f>
+        <v/>
+      </c>
+      <c r="K53" s="10">
+        <f>G53*GP_Nairne_Pct</f>
+        <v/>
+      </c>
+      <c r="L53" s="10">
+        <f>G53*GP_Alec_Pct</f>
         <v/>
       </c>
       <c r="M53" s="10">
         <f>ROUND(SUM(H53:L53)-G53, 2)</f>
+        <v/>
+      </c>
+      <c r="N53" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D54" s="15">
+        <f>SUM(D2:D53)</f>
+        <v/>
+      </c>
+      <c r="E54" s="15">
+        <f>SUM(E2:E53)</f>
+        <v/>
+      </c>
+      <c r="F54" s="15">
+        <f>SUM(F2:F53)</f>
+        <v/>
+      </c>
+      <c r="G54" s="15">
+        <f>SUM(G2:G53)</f>
+        <v/>
+      </c>
+      <c r="H54" s="15">
+        <f>SUM(H2:H53)</f>
+        <v/>
+      </c>
+      <c r="I54" s="15">
+        <f>SUM(I2:I53)</f>
+        <v/>
+      </c>
+      <c r="J54" s="15">
+        <f>SUM(J2:J53)</f>
+        <v/>
+      </c>
+      <c r="K54" s="15">
+        <f>SUM(K2:K53)</f>
+        <v/>
+      </c>
+      <c r="L54" s="15">
+        <f>SUM(L2:L53)</f>
+        <v/>
+      </c>
+      <c r="M54" s="10">
+        <f>ROUND(SUM(H54:L54)-G54, 2)</f>
+        <v/>
+      </c>
+      <c r="N54" s="16">
+        <f>SUM(N2:N53)</f>
         <v/>
       </c>
     </row>
@@ -4958,11 +5213,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -5013,8 +5268,8 @@
           <t>AJ Affleck</t>
         </is>
       </c>
-      <c r="B2">
-        <f>COUNTIF(PI_Consultant, A2)</f>
+      <c r="B2" s="17">
+        <f>SUMIF(PI_Consultant, A2, PI_Share)</f>
         <v/>
       </c>
       <c r="C2" s="10">
@@ -5025,8 +5280,8 @@
         <f>SUMIF(PI_Consultant, A2, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E2" s="13">
-        <f>IFERROR(D2/$D$14,0)</f>
+      <c r="E2" s="11">
+        <f>IFERROR(D2/$D$15,0)</f>
         <v/>
       </c>
       <c r="F2" s="10">
@@ -5044,8 +5299,8 @@
           <t>Alec Atkinson</t>
         </is>
       </c>
-      <c r="B3">
-        <f>COUNTIF(PI_Consultant, A3)</f>
+      <c r="B3" s="17">
+        <f>SUMIF(PI_Consultant, A3, PI_Share)</f>
         <v/>
       </c>
       <c r="C3" s="10">
@@ -5056,8 +5311,8 @@
         <f>SUMIF(PI_Consultant, A3, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E3" s="13">
-        <f>IFERROR(D3/$D$14,0)</f>
+      <c r="E3" s="11">
+        <f>IFERROR(D3/$D$15,0)</f>
         <v/>
       </c>
       <c r="F3" s="10">
@@ -5075,8 +5330,8 @@
           <t>Fund Hub SPV (Pending Split)</t>
         </is>
       </c>
-      <c r="B4">
-        <f>COUNTIF(PI_Consultant, A4)</f>
+      <c r="B4" s="17">
+        <f>SUMIF(PI_Consultant, A4, PI_Share)</f>
         <v/>
       </c>
       <c r="C4" s="10">
@@ -5087,8 +5342,8 @@
         <f>SUMIF(PI_Consultant, A4, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E4" s="13">
-        <f>IFERROR(D4/$D$14,0)</f>
+      <c r="E4" s="11">
+        <f>IFERROR(D4/$D$15,0)</f>
         <v/>
       </c>
       <c r="F4" s="10">
@@ -5106,8 +5361,8 @@
           <t>Jake Gordon</t>
         </is>
       </c>
-      <c r="B5">
-        <f>COUNTIF(PI_Consultant, A5)</f>
+      <c r="B5" s="17">
+        <f>SUMIF(PI_Consultant, A5, PI_Share)</f>
         <v/>
       </c>
       <c r="C5" s="10">
@@ -5118,8 +5373,8 @@
         <f>SUMIF(PI_Consultant, A5, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E5" s="13">
-        <f>IFERROR(D5/$D$14,0)</f>
+      <c r="E5" s="11">
+        <f>IFERROR(D5/$D$15,0)</f>
         <v/>
       </c>
       <c r="F5" s="10">
@@ -5137,8 +5392,8 @@
           <t>Luke</t>
         </is>
       </c>
-      <c r="B6">
-        <f>COUNTIF(PI_Consultant, A6)</f>
+      <c r="B6" s="17">
+        <f>SUMIF(PI_Consultant, A6, PI_Share)</f>
         <v/>
       </c>
       <c r="C6" s="10">
@@ -5149,8 +5404,8 @@
         <f>SUMIF(PI_Consultant, A6, PI_ConsultantCut)</f>
         <v/>
       </c>
-      <c r="E6" s="13">
-        <f>IFERROR(D6/$D$14,0)</f>
+      <c r="E6" s="11">
+        <f>IFERROR(D6/$D$15,0)</f>
         <v/>
       </c>
       <c r="F6" s="10">
@@ -5163,99 +5418,97 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Raj (Split)</t>
+        </is>
+      </c>
+      <c r="B7" s="17">
+        <f>SUMIF(PI_Consultant, A7, PI_Share)</f>
+        <v/>
+      </c>
+      <c r="C7" s="10">
+        <f>SUMIF(PI_Consultant, A7, PI_Capital)</f>
+        <v/>
+      </c>
+      <c r="D7" s="10">
+        <f>SUMIF(PI_Consultant, A7, PI_ConsultantCut)</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>IFERROR(D7/$D$15,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A7, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="10">
+        <f>D7-F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>CONSULTANTS SUBTOTAL</t>
         </is>
       </c>
-      <c r="B7" s="15">
-        <f>SUM(B2:B6)</f>
-        <v/>
-      </c>
-      <c r="C7" s="12">
-        <f>SUM(C2:C6)</f>
-        <v/>
-      </c>
-      <c r="D7" s="12">
-        <f>SUM(D2:D6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="16">
-        <f>IFERROR(D7/$D$14,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>SUM(F2:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12">
-        <f>SUM(G2:G6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="B8" s="19">
+        <f>SUM(B2:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="15">
+        <f>SUM(C2:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
+        <f>SUM(D2:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>IFERROR(D8/$D$15,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>SUM(F2:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>SUM(G2:G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>GP POOL — OTHER RECIPIENTS</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Fund Mgmt</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="10">
+      <c r="D11" s="10">
         <f>SUM(PI_PerfFee)*GP_FundMgmt_Pct</f>
         <v/>
       </c>
-      <c r="E10" s="13">
-        <f>IFERROR(D10/$D$14,0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="10">
-        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A10, Costs_PartyHeaders, 0)), 0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="10">
-        <f>D10-F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>Raj (GP fixed 0.5%)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="10">
-        <f>SUM(PI_PerfFee)*GP_Raj_Pct</f>
-        <v/>
-      </c>
-      <c r="E11" s="13">
-        <f>IFERROR(D11/$D$14,0)</f>
+      <c r="E11" s="11">
+        <f>IFERROR(D11/$D$15,0)</f>
         <v/>
       </c>
       <c r="F11" s="10">
@@ -5268,9 +5521,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Nairne (GP fixed 0.5%)</t>
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Raj (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5284,11 +5537,11 @@
         </is>
       </c>
       <c r="D12" s="10">
-        <f>SUM(PI_PerfFee)*GP_Nairne_Pct</f>
-        <v/>
-      </c>
-      <c r="E12" s="13">
-        <f>IFERROR(D12/$D$14,0)</f>
+        <f>SUM(PI_PerfFee)*GP_Raj_Pct</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>IFERROR(D12/$D$15,0)</f>
         <v/>
       </c>
       <c r="F12" s="10">
@@ -5301,9 +5554,9 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>Alec (GP fixed 0.5%)</t>
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Nairne (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5317,11 +5570,11 @@
         </is>
       </c>
       <c r="D13" s="10">
-        <f>SUM(PI_PerfFee)*GP_Alec_Pct</f>
-        <v/>
-      </c>
-      <c r="E13" s="13">
-        <f>IFERROR(D13/$D$14,0)</f>
+        <f>SUM(PI_PerfFee)*GP_Nairne_Pct</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>IFERROR(D13/$D$15,0)</f>
         <v/>
       </c>
       <c r="F13" s="10">
@@ -5334,92 +5587,125 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="10">
+        <f>SUM(PI_PerfFee)*GP_Alec_Pct</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>IFERROR(D14/$D$15,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A14, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="10">
+        <f>D14-F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>GP POOL TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="12">
-        <f>SUM(D2:D6)+SUM(D10:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>D14/$D$14</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
-        <f>SUM(F2:F6)+SUM(F10:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="12">
-        <f>D14-F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="15">
+        <f>SUM(D2:D7)+SUM(D11:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>D15/$D$15</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>SUM(F2:F7)+SUM(F11:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="15">
+        <f>D15-F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>EXTERNAL — TruQuant (18% upstream of Armada's books)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>TruQuant</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="10">
+      <c r="D18" s="10">
         <f>TQ_Income</f>
         <v/>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="10">
-        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A17, Costs_PartyHeaders, 0)), 0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="10">
-        <f>D17-F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="F18" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A18, Costs_PartyHeaders, 0)), 0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>D18-F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>GRAND TOTAL (Armada + TQ)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="12">
-        <f>D14+D17</f>
-        <v/>
-      </c>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="12">
-        <f>F14+F17</f>
-        <v/>
-      </c>
-      <c r="G19" s="12">
-        <f>D19-F19</f>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="15">
+        <f>D15+D18</f>
+        <v/>
+      </c>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="15">
+        <f>F15+F18</f>
+        <v/>
+      </c>
+      <c r="G20" s="15">
+        <f>D20-F20</f>
         <v/>
       </c>
     </row>
@@ -5434,7 +5720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5451,6 +5737,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5468,7 +5755,7 @@
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Payor Groups: 'TQ/Armada' = split among everyone (incl. TruQuant) by income share. 'Armada' = split among Armada parties only (excludes TruQuant) by income. 'Fund Management' = 100% Fund Mgmt.</t>
         </is>
@@ -5522,25 +5809,30 @@
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
+          <t>Raj (Split)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
           <t>Fund Mgmt</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>TruQuant</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Raj (GP fixed 0.5%)</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Nairne (GP fixed 0.5%)</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
         <is>
           <t>Alec (GP fixed 0.5%)</t>
         </is>
@@ -5556,13 +5848,13 @@
         <v>8000</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>TQ/Armada</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>125.29</v>
+        <v>117.13</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>1196.17</v>
@@ -5577,13 +5869,13 @@
         <v>32.54</v>
       </c>
       <c r="J6" s="10" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="K6" s="10" t="n">
         <v>2748.24</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="L6" s="10" t="n">
         <v>3381.1</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>23.09</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>23.09</v>
@@ -5591,6 +5883,9 @@
       <c r="N6" s="10" t="n">
         <v>23.09</v>
       </c>
+      <c r="O6" s="10" t="n">
+        <v>23.09</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5602,13 +5897,13 @@
         <v>1200</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Armada</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>32.55</v>
+        <v>30.43</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>310.77</v>
@@ -5623,13 +5918,13 @@
         <v>8.449999999999999</v>
       </c>
       <c r="J7" s="10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K7" s="10" t="n">
         <v>714</v>
       </c>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M7" s="10" t="n">
         <v>6</v>
@@ -5637,6 +5932,9 @@
       <c r="N7" s="10" t="n">
         <v>6</v>
       </c>
+      <c r="O7" s="10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5648,13 +5946,13 @@
         <v>3226.17</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>TQ/Armada</t>
         </is>
       </c>
       <c r="E8" s="10" t="n">
-        <v>50.53</v>
+        <v>47.24</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>482.38</v>
@@ -5669,13 +5967,13 @@
         <v>13.12</v>
       </c>
       <c r="J8" s="10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="K8" s="10" t="n">
         <v>1108.29</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="L8" s="10" t="n">
         <v>1363.5</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>9.31</v>
       </c>
       <c r="M8" s="10" t="n">
         <v>9.31</v>
@@ -5683,6 +5981,9 @@
       <c r="N8" s="10" t="n">
         <v>9.31</v>
       </c>
+      <c r="O8" s="10" t="n">
+        <v>9.31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5694,13 +5995,13 @@
         <v>4000</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Armada</t>
         </is>
       </c>
       <c r="E9" s="10" t="n">
-        <v>108.5</v>
+        <v>101.44</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>1035.89</v>
@@ -5715,13 +6016,13 @@
         <v>28.18</v>
       </c>
       <c r="J9" s="10" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>2380</v>
       </c>
-      <c r="K9" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" s="10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M9" s="10" t="n">
         <v>20</v>
@@ -5729,6 +6030,9 @@
       <c r="N9" s="10" t="n">
         <v>20</v>
       </c>
+      <c r="O9" s="10" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5740,7 +6044,7 @@
         <v>886</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Fund Management</t>
         </is>
@@ -5761,11 +6065,11 @@
         <v>0</v>
       </c>
       <c r="J10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="10" t="n">
         <v>886</v>
       </c>
-      <c r="K10" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" s="10" t="n">
         <v>0</v>
       </c>
@@ -5773,6 +6077,9 @@
         <v>0</v>
       </c>
       <c r="N10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5786,7 +6093,7 @@
         <v>1172</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Fund Management</t>
         </is>
@@ -5807,11 +6114,11 @@
         <v>0</v>
       </c>
       <c r="J11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10" t="n">
         <v>1172</v>
       </c>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" s="10" t="n">
         <v>0</v>
       </c>
@@ -5819,6 +6126,9 @@
         <v>0</v>
       </c>
       <c r="N11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5832,13 +6142,13 @@
         <v>6750</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>Armada</t>
         </is>
       </c>
       <c r="E12" s="10" t="n">
-        <v>183.1</v>
+        <v>171.18</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>1748.06</v>
@@ -5853,13 +6163,13 @@
         <v>47.55</v>
       </c>
       <c r="J12" s="10" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="K12" s="10" t="n">
         <v>4016.25</v>
       </c>
-      <c r="K12" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" s="10" t="n">
-        <v>33.75</v>
+        <v>0</v>
       </c>
       <c r="M12" s="10" t="n">
         <v>33.75</v>
@@ -5867,6 +6177,9 @@
       <c r="N12" s="10" t="n">
         <v>33.75</v>
       </c>
+      <c r="O12" s="10" t="n">
+        <v>33.75</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5878,13 +6191,13 @@
         <v>26000</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>Armada</t>
         </is>
       </c>
       <c r="E13" s="10" t="n">
-        <v>705.28</v>
+        <v>659.35</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>6733.29</v>
@@ -5899,13 +6212,13 @@
         <v>183.16</v>
       </c>
       <c r="J13" s="10" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="K13" s="10" t="n">
         <v>15470</v>
       </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" s="10" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="M13" s="10" t="n">
         <v>130</v>
@@ -5913,55 +6226,62 @@
       <c r="N13" s="10" t="n">
         <v>130</v>
       </c>
+      <c r="O13" s="10" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="15">
         <f>SUM(B6:B13)</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="15">
         <f>SUM(E6:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="15">
         <f>SUM(F6:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="15">
         <f>SUM(G6:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="15">
         <f>SUM(H6:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="15">
         <f>SUM(I6:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="15">
         <f>SUM(J6:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="15">
         <f>SUM(K6:K13)</f>
         <v/>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="15">
         <f>SUM(L6:L13)</f>
         <v/>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="15">
         <f>SUM(M6:M13)</f>
         <v/>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="15">
         <f>SUM(N6:N13)</f>
+        <v/>
+      </c>
+      <c r="O14" s="15">
+        <f>SUM(O6:O13)</f>
         <v/>
       </c>
     </row>
@@ -6001,13 +6321,13 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>3293.22</v>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>0.01566156528291167</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>0.02712606283373016</v>
+        <v>3078.76</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>0.01464165271041199</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0.02535955916524154</v>
       </c>
     </row>
     <row r="20">
@@ -6019,10 +6339,10 @@
       <c r="B20" s="10" t="n">
         <v>31440.36</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="11" t="n">
         <v>0.1495209636632215</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="11" t="n">
         <v>0.2589725217130014</v>
       </c>
     </row>
@@ -6035,10 +6355,10 @@
       <c r="B21" s="10" t="n">
         <v>3496.35</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="11" t="n">
         <v>0.01662761667864213</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="11" t="n">
         <v>0.02879927814700346</v>
       </c>
     </row>
@@ -6051,10 +6371,10 @@
       <c r="B22" s="10" t="n">
         <v>8262.459999999999</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="11" t="n">
         <v>0.03929378719646822</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="11" t="n">
         <v>0.06805742090349085</v>
       </c>
     </row>
@@ -6067,99 +6387,115 @@
       <c r="B23" s="10" t="n">
         <v>855.26</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="11" t="n">
         <v>0.004067353471748701</v>
       </c>
-      <c r="D23" s="13" t="n">
-        <v>0.007044716402774138</v>
+      <c r="D23" s="11" t="n">
+        <v>0.007044716402774139</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fund Mgmt</t>
+          <t>Raj (Split)</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>72235.50999999999</v>
-      </c>
-      <c r="C24" s="13" t="n">
-        <v>0.3435305521649496</v>
-      </c>
-      <c r="D24" s="13" t="n">
-        <v>0.595</v>
+        <v>214.46</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>0.001019912572499674</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>0.001766503668488624</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TruQuant</t>
+          <t>Fund Mgmt</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>88869.69</v>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>0.4226377274538662</v>
-      </c>
-      <c r="D25" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>72235.50999999999</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>0.3435305521649495</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>0.595</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Raj (GP fixed 0.5%)</t>
+          <t>TruQuant</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>607.02</v>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>0.002886811362730669</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>0.005</v>
+        <v>88869.69</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0.4226377274538662</v>
+      </c>
+      <c r="D26" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nairne (GP fixed 0.5%)</t>
+          <t>Raj (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
         <v>607.02</v>
       </c>
-      <c r="C27" s="13" t="n">
-        <v>0.002886811362730669</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>0.005</v>
+      <c r="C27" s="11" t="n">
+        <v>0.002886811362730668</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.004999999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alec (GP fixed 0.5%)</t>
+          <t>Nairne (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
         <v>607.02</v>
       </c>
-      <c r="C28" s="13" t="n">
-        <v>0.002886811362730669</v>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>0.005</v>
+      <c r="C28" s="11" t="n">
+        <v>0.002886811362730668</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>0.004999999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>607.02</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>0.002886811362730668</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.004999999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6171,7 +6507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6207,7 +6543,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Total GP Pool</t>
         </is>
@@ -6218,7 +6554,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Cash Distributed (this period)</t>
         </is>
@@ -6229,7 +6565,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Remaining in Pool</t>
         </is>
@@ -6297,8 +6633,8 @@
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="25" t="inlineStr"/>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr"/>
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -6336,8 +6672,8 @@
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="25" t="inlineStr"/>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr"/>
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>Payout</t>
         </is>
@@ -6371,8 +6707,8 @@
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="25" t="inlineStr"/>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>Payout</t>
         </is>
@@ -6403,12 +6739,12 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="15">
         <f>SUM(F10:F22)</f>
         <v/>
       </c>
@@ -6469,11 +6805,11 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A27, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D27" s="10">
@@ -6488,7 +6824,7 @@
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="28" t="inlineStr"/>
+      <c r="G27" s="32" t="inlineStr"/>
       <c r="H27">
         <f>IF(ROUND(F27,2)=0,"Settled",IF(ROUND(F27,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6501,11 +6837,11 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A28, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D28" s="10">
@@ -6520,7 +6856,7 @@
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="28" t="inlineStr"/>
+      <c r="G28" s="32" t="inlineStr"/>
       <c r="H28">
         <f>IF(ROUND(F28,2)=0,"Settled",IF(ROUND(F28,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6533,11 +6869,11 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A29, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D29" s="10">
@@ -6552,7 +6888,7 @@
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="28" t="inlineStr"/>
+      <c r="G29" s="32" t="inlineStr"/>
       <c r="H29">
         <f>IF(ROUND(F29,2)=0,"Settled",IF(ROUND(F29,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6565,11 +6901,11 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A30, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D30" s="10">
@@ -6584,7 +6920,7 @@
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="28" t="inlineStr"/>
+      <c r="G30" s="32" t="inlineStr"/>
       <c r="H30">
         <f>IF(ROUND(F30,2)=0,"Settled",IF(ROUND(F30,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6597,11 +6933,11 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A31, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D31" s="10">
@@ -6616,7 +6952,7 @@
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="28" t="inlineStr"/>
+      <c r="G31" s="32" t="inlineStr"/>
       <c r="H31">
         <f>IF(ROUND(F31,2)=0,"Settled",IF(ROUND(F31,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6625,15 +6961,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fund Mgmt</t>
+          <t>Raj (Split)</t>
         </is>
       </c>
       <c r="B32" s="10">
-        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A32, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D32" s="10">
@@ -6648,7 +6984,7 @@
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="28" t="inlineStr"/>
+      <c r="G32" s="32" t="inlineStr"/>
       <c r="H32">
         <f>IF(ROUND(F32,2)=0,"Settled",IF(ROUND(F32,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6657,15 +6993,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Raj (GP fixed 0.5%)</t>
+          <t>Fund Mgmt</t>
         </is>
       </c>
       <c r="B33" s="10">
-        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A33, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D33" s="10">
@@ -6680,7 +7016,7 @@
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="28" t="inlineStr"/>
+      <c r="G33" s="32" t="inlineStr"/>
       <c r="H33">
         <f>IF(ROUND(F33,2)=0,"Settled",IF(ROUND(F33,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6689,15 +7025,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nairne (GP fixed 0.5%)</t>
+          <t>Raj (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B34" s="10">
-        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A34, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D34" s="10">
@@ -6712,7 +7048,7 @@
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="28" t="inlineStr"/>
+      <c r="G34" s="32" t="inlineStr"/>
       <c r="H34">
         <f>IF(ROUND(F34,2)=0,"Settled",IF(ROUND(F34,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
@@ -6721,15 +7057,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alec (GP fixed 0.5%)</t>
+          <t>Nairne (GP fixed 0.5%)</t>
         </is>
       </c>
       <c r="B35" s="10">
-        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$19, 4, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$19, 6, FALSE), 0)</f>
+        <f>IFERROR(VLOOKUP(A35, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
         <v/>
       </c>
       <c r="D35" s="10">
@@ -6744,87 +7080,119 @@
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="28" t="inlineStr"/>
+      <c r="G35" s="32" t="inlineStr"/>
       <c r="H35">
         <f>IF(ROUND(F35,2)=0,"Settled",IF(ROUND(F35,2)&lt;0,"Overpaid","Outstanding"))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Alec (GP fixed 0.5%)</t>
+        </is>
+      </c>
+      <c r="B36" s="10">
+        <f>IFERROR(VLOOKUP(A36, 'Consultant Summary'!$A$2:$G$20, 4, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="10">
+        <f>IFERROR(VLOOKUP(A36, 'Consultant Summary'!$A$2:$G$20, 6, FALSE), 0)</f>
+        <v/>
+      </c>
+      <c r="D36" s="10">
+        <f>B36-C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="10">
+        <f>SUMIFS(Dist_Amount, Dist_Party, A36, Dist_Type, "Payout")</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>D36-E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="32" t="inlineStr"/>
+      <c r="H36">
+        <f>IF(ROUND(F36,2)=0,"Settled",IF(ROUND(F36,2)&lt;0,"Overpaid","Outstanding"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>TOTAL (Armada GP Pool)</t>
         </is>
       </c>
-      <c r="B36" s="12">
-        <f>SUM(B27:B35)</f>
-        <v/>
-      </c>
-      <c r="C36" s="12">
-        <f>SUM(C27:C35)</f>
-        <v/>
-      </c>
-      <c r="D36" s="12">
-        <f>SUM(D27:D35)</f>
-        <v/>
-      </c>
-      <c r="E36" s="12">
-        <f>SUM(E27:E35)</f>
-        <v/>
-      </c>
-      <c r="F36" s="12">
-        <f>SUM(F27:F35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="B37" s="15">
+        <f>SUM(B27:B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="15">
+        <f>SUM(C27:C36)</f>
+        <v/>
+      </c>
+      <c r="D37" s="15">
+        <f>SUM(D27:D36)</f>
+        <v/>
+      </c>
+      <c r="E37" s="15">
+        <f>SUM(E27:E36)</f>
+        <v/>
+      </c>
+      <c r="F37" s="15">
+        <f>SUM(F27:F36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>External (does not draw from this pool)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>TruQuant</t>
         </is>
       </c>
-      <c r="B38" s="10">
+      <c r="B39" s="10">
         <f>TQ_Income</f>
         <v/>
       </c>
-      <c r="C38" s="10">
-        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A38, Costs_PartyHeaders, 0)),0)</f>
-        <v/>
-      </c>
-      <c r="D38" s="10">
-        <f>B38-C38</f>
-        <v/>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="C39" s="10">
+        <f>IFERROR(INDEX(Costs_PartyTotals, MATCH(A39, Costs_PartyHeaders, 0)),0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="10">
+        <f>B39-C39</f>
+        <v/>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="24" t="inlineStr">
+      <c r="F39" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>External — TruQuant's 18% comes upstream of this pool. Their share of TQ/Armada costs is also paid externally.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t>Note: Expenses (vendor cash) reduce the pool but don't count toward any party's Cash Paid Out — only Payout-type distributions do. Cash Paid Out aggregates from the Distributions Log via SUMIFS on Type='Payout'. To record a new transfer, add a row in the Distributions Log above and the Settlement table updates automatically.</t>
         </is>
@@ -6833,7 +7201,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:I41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6861,17 +7229,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6900,7 +7268,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>'Per-Investor Allocation'!H53+'Per-Investor Allocation'!I53+'Per-Investor Allocation'!J53+'Per-Investor Allocation'!K53+'Per-Investor Allocation'!L53</f>
+        <f>'Per-Investor Allocation'!H54+'Per-Investor Allocation'!I54+'Per-Investor Allocation'!J54+'Per-Investor Allocation'!K54+'Per-Investor Allocation'!L54</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
